--- a/apps/CameraTrapProcessing/data/Species_Database.xlsx
+++ b/apps/CameraTrapProcessing/data/Species_Database.xlsx
@@ -5,19 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4745970543a8c0a1/Camphora/Data_analysis/CameraTrapProcessing/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4745970543a8c0a1/Camphora/Data_analysis/CamphoraToolkitHub_Git/apps/CameraTrapProcessing/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="497" documentId="8_{941C5DAD-8161-4CB8-BDDF-7B2D28A4A2BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE270E5B-AFA2-4CDF-BA13-1A3793AE2CB9}"/>
+  <xr:revisionPtr revIDLastSave="514" documentId="8_{941C5DAD-8161-4CB8-BDDF-7B2D28A4A2BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CEAB51C6-9426-49ED-9C9F-7CDCCD645C0C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Species_Database" sheetId="1" r:id="rId1"/>
     <sheet name="Edit_Log" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Species_Database!$A$1:$P$659</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Species_Database!$A$1:$P$660</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8300" uniqueCount="1599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8316" uniqueCount="1606">
   <si>
     <t>FolderSpeciesName</t>
   </si>
@@ -5005,6 +5005,27 @@
   </si>
   <si>
     <t>1. Added Unidentified insect and Unidentified insecta</t>
+  </si>
+  <si>
+    <t>Hirundo javanica</t>
+  </si>
+  <si>
+    <t>hirundo javanica</t>
+  </si>
+  <si>
+    <t>Hirundinidae</t>
+  </si>
+  <si>
+    <t>Hirundo</t>
+  </si>
+  <si>
+    <t>Pacific swallow</t>
+  </si>
+  <si>
+    <t>Swallows spp.</t>
+  </si>
+  <si>
+    <t>1. Added Hirundo javanica</t>
   </si>
 </sst>
 </file>
@@ -5209,10 +5230,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5494,7 +5511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P659"/>
+  <dimension ref="A1:P660"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.42578125" bestFit="1" customWidth="1"/>
@@ -23362,10 +23379,10 @@
     </row>
     <row r="358" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>648</v>
+        <v>1600</v>
       </c>
       <c r="B358" t="s">
-        <v>649</v>
+        <v>1599</v>
       </c>
       <c r="C358" t="s">
         <v>17</v>
@@ -23377,16 +23394,16 @@
         <v>19</v>
       </c>
       <c r="F358" t="s">
-        <v>650</v>
+        <v>1601</v>
       </c>
       <c r="G358" t="s">
-        <v>651</v>
+        <v>1602</v>
       </c>
       <c r="H358" t="s">
-        <v>652</v>
+        <v>505</v>
       </c>
       <c r="I358" t="s">
-        <v>653</v>
+        <v>1603</v>
       </c>
       <c r="J358" t="b">
         <v>0</v>
@@ -23395,13 +23412,13 @@
         <v>24</v>
       </c>
       <c r="L358" t="s">
-        <v>654</v>
+        <v>1604</v>
       </c>
       <c r="M358">
         <v>1</v>
       </c>
       <c r="N358" t="s">
-        <v>654</v>
+        <v>1604</v>
       </c>
       <c r="O358" t="s">
         <v>26</v>
@@ -23412,10 +23429,10 @@
     </row>
     <row r="359" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="B359" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="C359" t="s">
         <v>17</v>
@@ -23433,10 +23450,10 @@
         <v>651</v>
       </c>
       <c r="H359" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="I359" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="J359" t="b">
         <v>0</v>
@@ -23461,8 +23478,8 @@
       </c>
     </row>
     <row r="360" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A360" s="1" t="s">
-        <v>1180</v>
+      <c r="A360" t="s">
+        <v>655</v>
       </c>
       <c r="B360" t="s">
         <v>656</v>
@@ -23511,11 +23528,11 @@
       </c>
     </row>
     <row r="361" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A361" t="s">
-        <v>659</v>
+      <c r="A361" s="1" t="s">
+        <v>1180</v>
       </c>
       <c r="B361" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="C361" t="s">
         <v>17</v>
@@ -23533,10 +23550,10 @@
         <v>651</v>
       </c>
       <c r="H361" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="I361" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="J361" t="b">
         <v>0</v>
@@ -23562,10 +23579,10 @@
     </row>
     <row r="362" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="B362" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="C362" t="s">
         <v>17</v>
@@ -23582,11 +23599,11 @@
       <c r="G362" t="s">
         <v>651</v>
       </c>
-      <c r="H362" t="e">
-        <v>#N/A</v>
+      <c r="H362" t="s">
+        <v>661</v>
       </c>
       <c r="I362" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="J362" t="b">
         <v>0</v>
@@ -23612,7 +23629,7 @@
     </row>
     <row r="363" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B363" t="s">
         <v>664</v>
@@ -23662,7 +23679,7 @@
     </row>
     <row r="364" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>1554</v>
+        <v>665</v>
       </c>
       <c r="B364" t="s">
         <v>664</v>
@@ -23712,7 +23729,7 @@
     </row>
     <row r="365" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>666</v>
+        <v>1554</v>
       </c>
       <c r="B365" t="s">
         <v>664</v>
@@ -23762,7 +23779,7 @@
     </row>
     <row r="366" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B366" t="s">
         <v>664</v>
@@ -23812,107 +23829,107 @@
     </row>
     <row r="367" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B367" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="C367" t="s">
         <v>17</v>
       </c>
       <c r="D367" t="s">
-        <v>103</v>
+        <v>18</v>
       </c>
       <c r="E367" t="s">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="F367" t="s">
-        <v>326</v>
+        <v>650</v>
       </c>
       <c r="G367" t="s">
-        <v>670</v>
-      </c>
-      <c r="H367" t="s">
-        <v>168</v>
+        <v>651</v>
+      </c>
+      <c r="H367" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I367" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="J367" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K367" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="L367" t="s">
-        <v>330</v>
+        <v>654</v>
       </c>
       <c r="M367">
         <v>1</v>
       </c>
       <c r="N367" t="s">
-        <v>669</v>
+        <v>654</v>
       </c>
       <c r="O367" t="s">
-        <v>331</v>
+        <v>26</v>
       </c>
       <c r="P367" t="s">
-        <v>1303</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="368" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="B368" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="C368" t="s">
         <v>17</v>
       </c>
       <c r="D368" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="E368" t="s">
-        <v>19</v>
+        <v>132</v>
       </c>
       <c r="F368" t="s">
-        <v>358</v>
+        <v>326</v>
       </c>
       <c r="G368" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="H368" t="s">
-        <v>585</v>
+        <v>168</v>
       </c>
       <c r="I368" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="J368" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K368" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="L368" t="s">
-        <v>362</v>
+        <v>330</v>
       </c>
       <c r="M368">
         <v>1</v>
       </c>
       <c r="N368" t="s">
-        <v>362</v>
+        <v>669</v>
       </c>
       <c r="O368" t="s">
-        <v>26</v>
+        <v>331</v>
       </c>
       <c r="P368" t="s">
-        <v>1338</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="369" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="B369" t="s">
         <v>673</v>
@@ -23962,107 +23979,107 @@
     </row>
     <row r="370" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B370" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="C370" t="s">
         <v>17</v>
       </c>
       <c r="D370" t="s">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="E370" t="s">
-        <v>124</v>
+        <v>19</v>
       </c>
       <c r="F370" t="s">
-        <v>190</v>
+        <v>358</v>
       </c>
       <c r="G370" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="H370" t="s">
-        <v>680</v>
+        <v>585</v>
       </c>
       <c r="I370" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="J370" t="b">
         <v>0</v>
       </c>
       <c r="K370" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="L370" t="s">
-        <v>194</v>
+        <v>362</v>
       </c>
       <c r="M370">
         <v>1</v>
       </c>
       <c r="N370" t="s">
-        <v>194</v>
+        <v>362</v>
       </c>
       <c r="O370" t="s">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="P370" t="s">
-        <v>1320</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="371" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>1354</v>
+        <v>677</v>
       </c>
       <c r="B371" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="C371" t="s">
         <v>17</v>
       </c>
       <c r="D371" t="s">
-        <v>18</v>
+        <v>123</v>
       </c>
       <c r="E371" t="s">
-        <v>19</v>
+        <v>124</v>
       </c>
       <c r="F371" t="s">
-        <v>635</v>
+        <v>190</v>
       </c>
       <c r="G371" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="H371" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="I371" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="J371" t="b">
         <v>0</v>
       </c>
       <c r="K371" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="L371" t="s">
-        <v>639</v>
+        <v>194</v>
       </c>
       <c r="M371">
         <v>1</v>
       </c>
       <c r="N371" t="s">
-        <v>639</v>
+        <v>194</v>
       </c>
       <c r="O371" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="P371" t="s">
-        <v>1338</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="372" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>682</v>
+        <v>1354</v>
       </c>
       <c r="B372" t="s">
         <v>683</v>
@@ -24112,7 +24129,7 @@
     </row>
     <row r="373" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="B373" t="s">
         <v>683</v>
@@ -24162,10 +24179,10 @@
     </row>
     <row r="374" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B374" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="C374" t="s">
         <v>17</v>
@@ -24183,10 +24200,10 @@
         <v>684</v>
       </c>
       <c r="H374" t="s">
-        <v>637</v>
+        <v>685</v>
       </c>
       <c r="I374" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="J374" t="b">
         <v>0</v>
@@ -24212,10 +24229,10 @@
     </row>
     <row r="375" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>1563</v>
+        <v>688</v>
       </c>
       <c r="B375" t="s">
-        <v>1564</v>
+        <v>689</v>
       </c>
       <c r="C375" t="s">
         <v>17</v>
@@ -24230,13 +24247,13 @@
         <v>635</v>
       </c>
       <c r="G375" t="s">
-        <v>636</v>
+        <v>684</v>
       </c>
       <c r="H375" t="s">
-        <v>1565</v>
+        <v>637</v>
       </c>
       <c r="I375" t="s">
-        <v>1566</v>
+        <v>690</v>
       </c>
       <c r="J375" t="b">
         <v>0</v>
@@ -24262,10 +24279,10 @@
     </row>
     <row r="376" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>691</v>
+        <v>1563</v>
       </c>
       <c r="B376" t="s">
-        <v>692</v>
+        <v>1564</v>
       </c>
       <c r="C376" t="s">
         <v>17</v>
@@ -24280,13 +24297,13 @@
         <v>635</v>
       </c>
       <c r="G376" t="s">
-        <v>684</v>
-      </c>
-      <c r="H376" t="e">
-        <v>#N/A</v>
+        <v>636</v>
+      </c>
+      <c r="H376" t="s">
+        <v>1565</v>
       </c>
       <c r="I376" t="s">
-        <v>639</v>
+        <v>1566</v>
       </c>
       <c r="J376" t="b">
         <v>0</v>
@@ -24312,7 +24329,7 @@
     </row>
     <row r="377" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>1121</v>
+        <v>691</v>
       </c>
       <c r="B377" t="s">
         <v>692</v>
@@ -24362,7 +24379,7 @@
     </row>
     <row r="378" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>1129</v>
+        <v>1121</v>
       </c>
       <c r="B378" t="s">
         <v>692</v>
@@ -24412,10 +24429,10 @@
     </row>
     <row r="379" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>693</v>
+        <v>1129</v>
       </c>
       <c r="B379" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C379" t="s">
         <v>17</v>
@@ -24432,11 +24449,11 @@
       <c r="G379" t="s">
         <v>684</v>
       </c>
-      <c r="H379" t="s">
-        <v>695</v>
+      <c r="H379" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I379" t="s">
-        <v>696</v>
+        <v>639</v>
       </c>
       <c r="J379" t="b">
         <v>0</v>
@@ -24461,11 +24478,11 @@
       </c>
     </row>
     <row r="380" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A380" s="1" t="s">
-        <v>1555</v>
+      <c r="A380" t="s">
+        <v>693</v>
       </c>
       <c r="B380" t="s">
-        <v>1556</v>
+        <v>694</v>
       </c>
       <c r="C380" t="s">
         <v>17</v>
@@ -24474,19 +24491,19 @@
         <v>18</v>
       </c>
       <c r="E380" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F380" t="s">
-        <v>50</v>
+        <v>635</v>
       </c>
       <c r="G380" t="s">
-        <v>699</v>
+        <v>684</v>
       </c>
       <c r="H380" t="s">
-        <v>1557</v>
+        <v>695</v>
       </c>
       <c r="I380" t="s">
-        <v>1558</v>
+        <v>696</v>
       </c>
       <c r="J380" t="b">
         <v>0</v>
@@ -24495,27 +24512,27 @@
         <v>24</v>
       </c>
       <c r="L380" t="s">
-        <v>54</v>
+        <v>639</v>
       </c>
       <c r="M380">
         <v>1</v>
       </c>
       <c r="N380" t="s">
-        <v>54</v>
+        <v>639</v>
       </c>
       <c r="O380" t="s">
         <v>26</v>
       </c>
       <c r="P380" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="381" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
-        <v>1171</v>
+        <v>1555</v>
       </c>
       <c r="B381" t="s">
-        <v>698</v>
+        <v>1556</v>
       </c>
       <c r="C381" t="s">
         <v>17</v>
@@ -24533,10 +24550,10 @@
         <v>699</v>
       </c>
       <c r="H381" t="s">
-        <v>700</v>
+        <v>1557</v>
       </c>
       <c r="I381" t="s">
-        <v>701</v>
+        <v>1558</v>
       </c>
       <c r="J381" t="b">
         <v>0</v>
@@ -24561,8 +24578,8 @@
       </c>
     </row>
     <row r="382" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A382" t="s">
-        <v>697</v>
+      <c r="A382" s="1" t="s">
+        <v>1171</v>
       </c>
       <c r="B382" t="s">
         <v>698</v>
@@ -24612,60 +24629,60 @@
     </row>
     <row r="383" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
+        <v>697</v>
+      </c>
+      <c r="B383" t="s">
+        <v>698</v>
+      </c>
+      <c r="C383" t="s">
+        <v>17</v>
+      </c>
+      <c r="D383" t="s">
+        <v>18</v>
+      </c>
+      <c r="E383" t="s">
+        <v>49</v>
+      </c>
+      <c r="F383" t="s">
+        <v>50</v>
+      </c>
+      <c r="G383" t="s">
+        <v>699</v>
+      </c>
+      <c r="H383" t="s">
+        <v>700</v>
+      </c>
+      <c r="I383" t="s">
+        <v>701</v>
+      </c>
+      <c r="J383" t="b">
+        <v>0</v>
+      </c>
+      <c r="K383" t="s">
+        <v>24</v>
+      </c>
+      <c r="L383" t="s">
+        <v>54</v>
+      </c>
+      <c r="M383">
+        <v>1</v>
+      </c>
+      <c r="N383" t="s">
+        <v>54</v>
+      </c>
+      <c r="O383" t="s">
+        <v>26</v>
+      </c>
+      <c r="P383" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="384" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
         <v>702</v>
       </c>
-      <c r="B383" t="s">
+      <c r="B384" t="s">
         <v>703</v>
-      </c>
-      <c r="C383" t="s">
-        <v>17</v>
-      </c>
-      <c r="D383" t="s">
-        <v>103</v>
-      </c>
-      <c r="E383" t="s">
-        <v>104</v>
-      </c>
-      <c r="F383" t="s">
-        <v>704</v>
-      </c>
-      <c r="G383" t="s">
-        <v>705</v>
-      </c>
-      <c r="H383" t="s">
-        <v>706</v>
-      </c>
-      <c r="I383" t="s">
-        <v>707</v>
-      </c>
-      <c r="J383" t="b">
-        <v>1</v>
-      </c>
-      <c r="K383" t="s">
-        <v>109</v>
-      </c>
-      <c r="L383" t="s">
-        <v>708</v>
-      </c>
-      <c r="M383">
-        <v>1</v>
-      </c>
-      <c r="N383" t="s">
-        <v>703</v>
-      </c>
-      <c r="O383" t="s">
-        <v>111</v>
-      </c>
-      <c r="P383" t="s">
-        <v>1325</v>
-      </c>
-    </row>
-    <row r="384" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A384" s="1" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B384" t="s">
-        <v>720</v>
       </c>
       <c r="C384" t="s">
         <v>17</v>
@@ -24683,10 +24700,10 @@
         <v>705</v>
       </c>
       <c r="H384" t="s">
-        <v>721</v>
+        <v>706</v>
       </c>
       <c r="I384" t="s">
-        <v>722</v>
+        <v>707</v>
       </c>
       <c r="J384" t="b">
         <v>1</v>
@@ -24701,7 +24718,7 @@
         <v>1</v>
       </c>
       <c r="N384" t="s">
-        <v>720</v>
+        <v>703</v>
       </c>
       <c r="O384" t="s">
         <v>111</v>
@@ -24711,8 +24728,8 @@
       </c>
     </row>
     <row r="385" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A385" t="s">
-        <v>719</v>
+      <c r="A385" s="1" t="s">
+        <v>1182</v>
       </c>
       <c r="B385" t="s">
         <v>720</v>
@@ -24761,8 +24778,8 @@
       </c>
     </row>
     <row r="386" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A386" s="1" t="s">
-        <v>1185</v>
+      <c r="A386" t="s">
+        <v>719</v>
       </c>
       <c r="B386" t="s">
         <v>720</v>
@@ -24812,7 +24829,7 @@
     </row>
     <row r="387" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="B387" t="s">
         <v>720</v>
@@ -24861,8 +24878,8 @@
       </c>
     </row>
     <row r="388" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A388" t="s">
-        <v>723</v>
+      <c r="A388" s="1" t="s">
+        <v>1186</v>
       </c>
       <c r="B388" t="s">
         <v>720</v>
@@ -24912,10 +24929,10 @@
     </row>
     <row r="389" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B389" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="C389" t="s">
         <v>17</v>
@@ -24933,10 +24950,10 @@
         <v>705</v>
       </c>
       <c r="H389" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="I389" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="J389" t="b">
         <v>1</v>
@@ -24951,7 +24968,7 @@
         <v>1</v>
       </c>
       <c r="N389" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="O389" t="s">
         <v>111</v>
@@ -24962,10 +24979,10 @@
     </row>
     <row r="390" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="B390" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="C390" t="s">
         <v>17</v>
@@ -24977,16 +24994,16 @@
         <v>104</v>
       </c>
       <c r="F390" t="s">
-        <v>105</v>
+        <v>704</v>
       </c>
       <c r="G390" t="s">
-        <v>730</v>
+        <v>705</v>
       </c>
       <c r="H390" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="I390" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="J390" t="b">
         <v>1</v>
@@ -24995,77 +25012,77 @@
         <v>109</v>
       </c>
       <c r="L390" t="s">
-        <v>110</v>
+        <v>708</v>
       </c>
       <c r="M390">
         <v>1</v>
       </c>
       <c r="N390" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="O390" t="s">
         <v>111</v>
       </c>
       <c r="P390" t="s">
-        <v>1322</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="391" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="B391" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="C391" t="s">
         <v>17</v>
       </c>
       <c r="D391" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="E391" t="s">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="F391" t="s">
-        <v>735</v>
+        <v>105</v>
       </c>
       <c r="G391" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="H391" t="s">
-        <v>505</v>
+        <v>731</v>
       </c>
       <c r="I391" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="J391" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K391" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="L391" t="s">
-        <v>738</v>
+        <v>110</v>
       </c>
       <c r="M391">
         <v>1</v>
       </c>
       <c r="N391" t="s">
-        <v>738</v>
+        <v>729</v>
       </c>
       <c r="O391" t="s">
-        <v>26</v>
+        <v>111</v>
       </c>
       <c r="P391" t="s">
-        <v>1338</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="392" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="B392" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="C392" t="s">
         <v>17</v>
@@ -25077,16 +25094,16 @@
         <v>19</v>
       </c>
       <c r="F392" t="s">
-        <v>635</v>
+        <v>735</v>
       </c>
       <c r="G392" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="H392" t="s">
-        <v>742</v>
+        <v>505</v>
       </c>
       <c r="I392" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="J392" t="b">
         <v>0</v>
@@ -25095,13 +25112,13 @@
         <v>24</v>
       </c>
       <c r="L392" t="s">
-        <v>639</v>
+        <v>738</v>
       </c>
       <c r="M392">
         <v>1</v>
       </c>
       <c r="N392" t="s">
-        <v>639</v>
+        <v>738</v>
       </c>
       <c r="O392" t="s">
         <v>26</v>
@@ -25112,107 +25129,107 @@
     </row>
     <row r="393" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>1289</v>
+        <v>739</v>
       </c>
       <c r="B393" t="s">
-        <v>1290</v>
+        <v>740</v>
       </c>
       <c r="C393" t="s">
         <v>17</v>
       </c>
       <c r="D393" t="s">
-        <v>103</v>
+        <v>18</v>
       </c>
       <c r="E393" t="s">
-        <v>788</v>
+        <v>19</v>
       </c>
       <c r="F393" t="s">
-        <v>1291</v>
+        <v>635</v>
       </c>
       <c r="G393" t="s">
-        <v>1292</v>
+        <v>741</v>
       </c>
       <c r="H393" t="s">
-        <v>1293</v>
+        <v>742</v>
       </c>
       <c r="I393" t="s">
-        <v>1294</v>
+        <v>743</v>
       </c>
       <c r="J393" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K393" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="L393" t="s">
-        <v>1290</v>
+        <v>639</v>
       </c>
       <c r="M393">
         <v>1</v>
       </c>
       <c r="N393" t="s">
-        <v>1290</v>
+        <v>639</v>
       </c>
       <c r="O393" t="s">
-        <v>339</v>
+        <v>26</v>
       </c>
       <c r="P393" t="s">
-        <v>1296</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="394" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>1533</v>
+        <v>1289</v>
       </c>
       <c r="B394" t="s">
-        <v>1273</v>
+        <v>1290</v>
       </c>
       <c r="C394" t="s">
         <v>17</v>
       </c>
       <c r="D394" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="E394" t="s">
-        <v>124</v>
+        <v>788</v>
       </c>
       <c r="F394" t="s">
-        <v>302</v>
-      </c>
-      <c r="G394" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H394" t="e">
-        <v>#N/A</v>
+        <v>1291</v>
+      </c>
+      <c r="G394" t="s">
+        <v>1292</v>
+      </c>
+      <c r="H394" t="s">
+        <v>1293</v>
       </c>
       <c r="I394" t="s">
-        <v>958</v>
+        <v>1294</v>
       </c>
       <c r="J394" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K394" t="s">
         <v>109</v>
       </c>
       <c r="L394" t="s">
-        <v>306</v>
+        <v>1290</v>
       </c>
       <c r="M394">
         <v>1</v>
       </c>
       <c r="N394" t="s">
-        <v>306</v>
+        <v>1290</v>
       </c>
       <c r="O394" t="s">
-        <v>95</v>
+        <v>339</v>
       </c>
       <c r="P394" t="s">
-        <v>1321</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="395" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A395" s="1" t="s">
-        <v>1188</v>
+      <c r="A395" t="s">
+        <v>1533</v>
       </c>
       <c r="B395" t="s">
         <v>1273</v>
@@ -25262,7 +25279,7 @@
     </row>
     <row r="396" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
-        <v>1347</v>
+        <v>1188</v>
       </c>
       <c r="B396" t="s">
         <v>1273</v>
@@ -25312,7 +25329,7 @@
     </row>
     <row r="397" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="B397" t="s">
         <v>1273</v>
@@ -25362,7 +25379,7 @@
     </row>
     <row r="398" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="B398" t="s">
         <v>1273</v>
@@ -25411,58 +25428,58 @@
       </c>
     </row>
     <row r="399" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A399" t="s">
-        <v>744</v>
+      <c r="A399" s="1" t="s">
+        <v>1346</v>
       </c>
       <c r="B399" t="s">
-        <v>745</v>
+        <v>1273</v>
       </c>
       <c r="C399" t="s">
         <v>17</v>
       </c>
       <c r="D399" t="s">
-        <v>18</v>
+        <v>123</v>
       </c>
       <c r="E399" t="s">
-        <v>180</v>
+        <v>124</v>
       </c>
       <c r="F399" t="s">
-        <v>181</v>
-      </c>
-      <c r="G399" t="s">
-        <v>746</v>
-      </c>
-      <c r="H399" t="s">
-        <v>585</v>
+        <v>302</v>
+      </c>
+      <c r="G399" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H399" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I399" t="s">
-        <v>747</v>
+        <v>958</v>
       </c>
       <c r="J399" t="b">
         <v>0</v>
       </c>
       <c r="K399" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="L399" t="s">
-        <v>185</v>
+        <v>306</v>
       </c>
       <c r="M399">
         <v>1</v>
       </c>
       <c r="N399" t="s">
-        <v>185</v>
+        <v>306</v>
       </c>
       <c r="O399" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="P399" t="s">
-        <v>1333</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="400" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B400" t="s">
         <v>745</v>
@@ -25512,7 +25529,7 @@
     </row>
     <row r="401" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B401" t="s">
         <v>745</v>
@@ -25562,10 +25579,10 @@
     </row>
     <row r="402" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B402" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="C402" t="s">
         <v>17</v>
@@ -25589,10 +25606,10 @@
         <v>747</v>
       </c>
       <c r="J402" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K402" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="L402" t="s">
         <v>185</v>
@@ -25612,10 +25629,10 @@
     </row>
     <row r="403" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B403" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C403" t="s">
         <v>17</v>
@@ -25630,19 +25647,19 @@
         <v>181</v>
       </c>
       <c r="G403" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="H403" t="s">
-        <v>755</v>
+        <v>585</v>
       </c>
       <c r="I403" t="s">
-        <v>756</v>
+        <v>747</v>
       </c>
       <c r="J403" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K403" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="L403" t="s">
         <v>185</v>
@@ -25662,10 +25679,10 @@
     </row>
     <row r="404" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="B404" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="C404" t="s">
         <v>17</v>
@@ -25674,19 +25691,19 @@
         <v>18</v>
       </c>
       <c r="E404" t="s">
-        <v>442</v>
+        <v>180</v>
       </c>
       <c r="F404" t="s">
-        <v>443</v>
+        <v>181</v>
       </c>
       <c r="G404" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="H404" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="I404" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="J404" t="b">
         <v>0</v>
@@ -25695,74 +25712,74 @@
         <v>24</v>
       </c>
       <c r="L404" t="s">
-        <v>447</v>
+        <v>185</v>
       </c>
       <c r="M404">
         <v>1</v>
       </c>
       <c r="N404" t="s">
-        <v>447</v>
+        <v>185</v>
       </c>
       <c r="O404" t="s">
         <v>26</v>
       </c>
       <c r="P404" t="s">
-        <v>1341</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="405" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="B405" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="C405" t="s">
         <v>17</v>
       </c>
       <c r="D405" t="s">
-        <v>103</v>
+        <v>18</v>
       </c>
       <c r="E405" t="s">
-        <v>764</v>
+        <v>442</v>
       </c>
       <c r="F405" t="s">
-        <v>765</v>
+        <v>443</v>
       </c>
       <c r="G405" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
       <c r="H405" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
       <c r="I405" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="J405" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K405" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="L405" t="s">
-        <v>110</v>
+        <v>447</v>
       </c>
       <c r="M405">
         <v>1</v>
       </c>
       <c r="N405" t="s">
-        <v>763</v>
+        <v>447</v>
       </c>
       <c r="O405" t="s">
-        <v>111</v>
+        <v>26</v>
       </c>
       <c r="P405" t="s">
-        <v>1326</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="406" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>1507</v>
+        <v>762</v>
       </c>
       <c r="B406" t="s">
         <v>763</v>
@@ -25812,10 +25829,10 @@
     </row>
     <row r="407" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>769</v>
+        <v>1507</v>
       </c>
       <c r="B407" t="s">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="C407" t="s">
         <v>17</v>
@@ -25824,19 +25841,19 @@
         <v>103</v>
       </c>
       <c r="E407" t="s">
-        <v>104</v>
+        <v>764</v>
       </c>
       <c r="F407" t="s">
-        <v>704</v>
+        <v>765</v>
       </c>
       <c r="G407" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="H407" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="I407" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="J407" t="b">
         <v>1</v>
@@ -25845,24 +25862,24 @@
         <v>109</v>
       </c>
       <c r="L407" t="s">
-        <v>708</v>
+        <v>110</v>
       </c>
       <c r="M407">
         <v>1</v>
       </c>
       <c r="N407" t="s">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="O407" t="s">
         <v>111</v>
       </c>
       <c r="P407" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="408" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A408" s="1" t="s">
-        <v>1183</v>
+      <c r="A408" t="s">
+        <v>769</v>
       </c>
       <c r="B408" t="s">
         <v>770</v>
@@ -25911,8 +25928,8 @@
       </c>
     </row>
     <row r="409" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A409" t="s">
-        <v>774</v>
+      <c r="A409" s="1" t="s">
+        <v>1183</v>
       </c>
       <c r="B409" t="s">
         <v>770</v>
@@ -25962,7 +25979,7 @@
     </row>
     <row r="410" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B410" t="s">
         <v>770</v>
@@ -26011,8 +26028,8 @@
       </c>
     </row>
     <row r="411" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A411" s="1" t="s">
-        <v>1184</v>
+      <c r="A411" t="s">
+        <v>775</v>
       </c>
       <c r="B411" t="s">
         <v>770</v>
@@ -26061,8 +26078,8 @@
       </c>
     </row>
     <row r="412" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A412" t="s">
-        <v>776</v>
+      <c r="A412" s="1" t="s">
+        <v>1184</v>
       </c>
       <c r="B412" t="s">
         <v>770</v>
@@ -26112,7 +26129,7 @@
     </row>
     <row r="413" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B413" t="s">
         <v>770</v>
@@ -26162,7 +26179,7 @@
     </row>
     <row r="414" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B414" t="s">
         <v>770</v>
@@ -26212,7 +26229,7 @@
     </row>
     <row r="415" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B415" t="s">
         <v>770</v>
@@ -26262,10 +26279,10 @@
     </row>
     <row r="416" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B416" t="s">
-        <v>781</v>
+        <v>770</v>
       </c>
       <c r="C416" t="s">
         <v>17</v>
@@ -26277,16 +26294,16 @@
         <v>104</v>
       </c>
       <c r="F416" t="s">
-        <v>105</v>
+        <v>704</v>
       </c>
       <c r="G416" t="s">
-        <v>782</v>
+        <v>771</v>
       </c>
       <c r="H416" t="s">
-        <v>783</v>
+        <v>772</v>
       </c>
       <c r="I416" t="s">
-        <v>784</v>
+        <v>773</v>
       </c>
       <c r="J416" t="b">
         <v>1</v>
@@ -26295,24 +26312,24 @@
         <v>109</v>
       </c>
       <c r="L416" t="s">
-        <v>110</v>
+        <v>708</v>
       </c>
       <c r="M416">
         <v>1</v>
       </c>
       <c r="N416" t="s">
-        <v>781</v>
+        <v>770</v>
       </c>
       <c r="O416" t="s">
         <v>111</v>
       </c>
       <c r="P416" t="s">
-        <v>1322</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="417" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="B417" t="s">
         <v>781</v>
@@ -26362,10 +26379,10 @@
     </row>
     <row r="418" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>1536</v>
+        <v>785</v>
       </c>
       <c r="B418" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="C418" t="s">
         <v>17</v>
@@ -26374,19 +26391,19 @@
         <v>103</v>
       </c>
       <c r="E418" t="s">
-        <v>788</v>
+        <v>104</v>
       </c>
       <c r="F418" t="s">
-        <v>789</v>
+        <v>105</v>
       </c>
       <c r="G418" t="s">
-        <v>790</v>
+        <v>782</v>
       </c>
       <c r="H418" t="s">
-        <v>791</v>
+        <v>783</v>
       </c>
       <c r="I418" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="J418" t="b">
         <v>1</v>
@@ -26395,24 +26412,24 @@
         <v>109</v>
       </c>
       <c r="L418" t="s">
-        <v>787</v>
+        <v>110</v>
       </c>
       <c r="M418">
         <v>1</v>
       </c>
       <c r="N418" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="O418" t="s">
-        <v>787</v>
+        <v>111</v>
       </c>
       <c r="P418" t="s">
-        <v>1318</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="419" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A419" s="1" t="s">
-        <v>1179</v>
+      <c r="A419" t="s">
+        <v>1536</v>
       </c>
       <c r="B419" t="s">
         <v>787</v>
@@ -26461,8 +26478,8 @@
       </c>
     </row>
     <row r="420" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A420" t="s">
-        <v>786</v>
+      <c r="A420" s="1" t="s">
+        <v>1179</v>
       </c>
       <c r="B420" t="s">
         <v>787</v>
@@ -26511,8 +26528,8 @@
       </c>
     </row>
     <row r="421" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A421" s="1" t="s">
-        <v>1191</v>
+      <c r="A421" t="s">
+        <v>786</v>
       </c>
       <c r="B421" t="s">
         <v>787</v>
@@ -26562,81 +26579,81 @@
     </row>
     <row r="422" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B422" t="s">
+        <v>787</v>
+      </c>
+      <c r="C422" t="s">
+        <v>17</v>
+      </c>
+      <c r="D422" t="s">
+        <v>103</v>
+      </c>
+      <c r="E422" t="s">
+        <v>788</v>
+      </c>
+      <c r="F422" t="s">
+        <v>789</v>
+      </c>
+      <c r="G422" t="s">
+        <v>790</v>
+      </c>
+      <c r="H422" t="s">
+        <v>791</v>
+      </c>
+      <c r="I422" t="s">
+        <v>792</v>
+      </c>
+      <c r="J422" t="b">
+        <v>1</v>
+      </c>
+      <c r="K422" t="s">
+        <v>109</v>
+      </c>
+      <c r="L422" t="s">
+        <v>787</v>
+      </c>
+      <c r="M422">
+        <v>1</v>
+      </c>
+      <c r="N422" t="s">
+        <v>787</v>
+      </c>
+      <c r="O422" t="s">
+        <v>787</v>
+      </c>
+      <c r="P422" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="423" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A423" s="1" t="s">
         <v>1165</v>
       </c>
-      <c r="B422" t="s">
+      <c r="B423" t="s">
         <v>1262</v>
       </c>
-      <c r="C422" t="s">
-        <v>17</v>
-      </c>
-      <c r="D422" t="s">
+      <c r="C423" t="s">
+        <v>17</v>
+      </c>
+      <c r="D423" t="s">
         <v>87</v>
       </c>
-      <c r="E422" t="s">
+      <c r="E423" t="s">
         <v>296</v>
       </c>
-      <c r="F422" t="s">
+      <c r="F423" t="s">
         <v>432</v>
       </c>
-      <c r="G422" t="s">
+      <c r="G423" t="s">
         <v>1263</v>
       </c>
-      <c r="H422" t="s">
+      <c r="H423" t="s">
         <v>1264</v>
       </c>
-      <c r="I422" t="s">
+      <c r="I423" t="s">
         <v>1265</v>
-      </c>
-      <c r="J422" t="b">
-        <v>0</v>
-      </c>
-      <c r="K422" t="s">
-        <v>24</v>
-      </c>
-      <c r="L422" t="s">
-        <v>93</v>
-      </c>
-      <c r="M422">
-        <v>1</v>
-      </c>
-      <c r="N422" t="s">
-        <v>94</v>
-      </c>
-      <c r="O422" t="s">
-        <v>95</v>
-      </c>
-      <c r="P422" t="s">
-        <v>1310</v>
-      </c>
-    </row>
-    <row r="423" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A423" t="s">
-        <v>793</v>
-      </c>
-      <c r="B423" t="s">
-        <v>794</v>
-      </c>
-      <c r="C423" t="s">
-        <v>17</v>
-      </c>
-      <c r="D423" t="s">
-        <v>18</v>
-      </c>
-      <c r="E423" t="s">
-        <v>19</v>
-      </c>
-      <c r="F423" t="s">
-        <v>795</v>
-      </c>
-      <c r="G423" t="s">
-        <v>796</v>
-      </c>
-      <c r="H423" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I423" t="s">
-        <v>797</v>
       </c>
       <c r="J423" t="b">
         <v>0</v>
@@ -26645,27 +26662,27 @@
         <v>24</v>
       </c>
       <c r="L423" t="s">
-        <v>798</v>
+        <v>93</v>
       </c>
       <c r="M423">
         <v>1</v>
       </c>
       <c r="N423" t="s">
-        <v>798</v>
+        <v>94</v>
       </c>
       <c r="O423" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="P423" t="s">
-        <v>1338</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="424" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="B424" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="C424" t="s">
         <v>17</v>
@@ -26674,19 +26691,19 @@
         <v>18</v>
       </c>
       <c r="E424" t="s">
-        <v>405</v>
+        <v>19</v>
       </c>
       <c r="F424" t="s">
-        <v>400</v>
+        <v>795</v>
       </c>
       <c r="G424" t="s">
-        <v>801</v>
-      </c>
-      <c r="H424" t="s">
-        <v>802</v>
+        <v>796</v>
+      </c>
+      <c r="H424" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I424" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="J424" t="b">
         <v>0</v>
@@ -26695,24 +26712,24 @@
         <v>24</v>
       </c>
       <c r="L424" t="s">
-        <v>402</v>
+        <v>798</v>
       </c>
       <c r="M424">
         <v>1</v>
       </c>
       <c r="N424" t="s">
-        <v>402</v>
+        <v>798</v>
       </c>
       <c r="O424" t="s">
         <v>26</v>
       </c>
       <c r="P424" t="s">
-        <v>1334</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="425" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A425" s="1" t="s">
-        <v>1192</v>
+      <c r="A425" t="s">
+        <v>799</v>
       </c>
       <c r="B425" t="s">
         <v>800</v>
@@ -26761,58 +26778,58 @@
       </c>
     </row>
     <row r="426" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A426" t="s">
-        <v>1399</v>
+      <c r="A426" s="1" t="s">
+        <v>1192</v>
       </c>
       <c r="B426" t="s">
-        <v>1402</v>
+        <v>800</v>
       </c>
       <c r="C426" t="s">
         <v>17</v>
       </c>
       <c r="D426" t="s">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="E426" t="s">
-        <v>236</v>
+        <v>405</v>
       </c>
       <c r="F426" t="s">
-        <v>1404</v>
+        <v>400</v>
       </c>
       <c r="G426" t="s">
-        <v>1401</v>
+        <v>801</v>
       </c>
       <c r="H426" t="s">
-        <v>1400</v>
+        <v>802</v>
       </c>
       <c r="I426" t="s">
-        <v>1405</v>
+        <v>803</v>
       </c>
       <c r="J426" t="b">
         <v>0</v>
       </c>
       <c r="K426" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="L426" t="s">
-        <v>241</v>
+        <v>402</v>
       </c>
       <c r="M426">
         <v>1</v>
       </c>
       <c r="N426" t="s">
-        <v>241</v>
+        <v>402</v>
       </c>
       <c r="O426" t="s">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="P426" t="s">
-        <v>1356</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="427" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>1409</v>
+        <v>1399</v>
       </c>
       <c r="B427" t="s">
         <v>1402</v>
@@ -26862,60 +26879,60 @@
     </row>
     <row r="428" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>804</v>
+        <v>1409</v>
       </c>
       <c r="B428" t="s">
-        <v>805</v>
+        <v>1402</v>
       </c>
       <c r="C428" t="s">
         <v>17</v>
       </c>
       <c r="D428" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="E428" t="s">
-        <v>788</v>
+        <v>236</v>
       </c>
       <c r="F428" t="s">
-        <v>806</v>
+        <v>1404</v>
       </c>
       <c r="G428" t="s">
-        <v>807</v>
+        <v>1401</v>
       </c>
       <c r="H428" t="s">
-        <v>808</v>
+        <v>1400</v>
       </c>
       <c r="I428" t="s">
-        <v>809</v>
+        <v>1405</v>
       </c>
       <c r="J428" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K428" t="s">
         <v>109</v>
       </c>
       <c r="L428" t="s">
-        <v>810</v>
+        <v>241</v>
       </c>
       <c r="M428">
         <v>1</v>
       </c>
       <c r="N428" t="s">
-        <v>810</v>
+        <v>241</v>
       </c>
       <c r="O428" t="s">
-        <v>810</v>
+        <v>95</v>
       </c>
       <c r="P428" t="s">
-        <v>1317</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="429" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
       <c r="B429" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
       <c r="C429" t="s">
         <v>17</v>
@@ -26933,10 +26950,10 @@
         <v>807</v>
       </c>
       <c r="H429" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="I429" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="J429" t="b">
         <v>1</v>
@@ -26962,10 +26979,10 @@
     </row>
     <row r="430" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>1275</v>
+        <v>811</v>
       </c>
       <c r="B430" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C430" t="s">
         <v>17</v>
@@ -26982,11 +26999,11 @@
       <c r="G430" t="s">
         <v>807</v>
       </c>
-      <c r="H430" t="e">
-        <v>#N/A</v>
+      <c r="H430" t="s">
+        <v>813</v>
       </c>
       <c r="I430" t="s">
-        <v>1283</v>
+        <v>814</v>
       </c>
       <c r="J430" t="b">
         <v>1</v>
@@ -27012,107 +27029,107 @@
     </row>
     <row r="431" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>815</v>
+        <v>1275</v>
       </c>
       <c r="B431" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="C431" t="s">
         <v>17</v>
       </c>
       <c r="D431" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="E431" t="s">
-        <v>180</v>
+        <v>788</v>
       </c>
       <c r="F431" t="s">
-        <v>181</v>
+        <v>806</v>
       </c>
       <c r="G431" t="s">
-        <v>817</v>
-      </c>
-      <c r="H431" t="s">
-        <v>818</v>
+        <v>807</v>
+      </c>
+      <c r="H431" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I431" t="s">
-        <v>819</v>
+        <v>1283</v>
       </c>
       <c r="J431" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K431" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="L431" t="s">
-        <v>185</v>
+        <v>810</v>
       </c>
       <c r="M431">
         <v>1</v>
       </c>
       <c r="N431" t="s">
-        <v>185</v>
+        <v>810</v>
       </c>
       <c r="O431" t="s">
-        <v>26</v>
+        <v>810</v>
       </c>
       <c r="P431" t="s">
-        <v>1333</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="432" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>1535</v>
+        <v>815</v>
       </c>
       <c r="B432" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="C432" t="s">
         <v>17</v>
       </c>
       <c r="D432" t="s">
-        <v>103</v>
+        <v>18</v>
       </c>
       <c r="E432" t="s">
-        <v>822</v>
+        <v>180</v>
       </c>
       <c r="F432" t="s">
-        <v>823</v>
+        <v>181</v>
       </c>
       <c r="G432" t="s">
-        <v>824</v>
+        <v>817</v>
       </c>
       <c r="H432" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
       <c r="I432" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
       <c r="J432" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K432" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="L432" t="s">
-        <v>110</v>
+        <v>185</v>
       </c>
       <c r="M432">
         <v>1</v>
       </c>
       <c r="N432" t="s">
-        <v>821</v>
+        <v>185</v>
       </c>
       <c r="O432" t="s">
-        <v>111</v>
+        <v>26</v>
       </c>
       <c r="P432" t="s">
-        <v>1319</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="433" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="B433" t="s">
         <v>821</v>
@@ -27161,8 +27178,8 @@
       </c>
     </row>
     <row r="434" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A434" s="1" t="s">
-        <v>1172</v>
+      <c r="A434" t="s">
+        <v>1534</v>
       </c>
       <c r="B434" t="s">
         <v>821</v>
@@ -27211,8 +27228,8 @@
       </c>
     </row>
     <row r="435" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A435" t="s">
-        <v>820</v>
+      <c r="A435" s="1" t="s">
+        <v>1172</v>
       </c>
       <c r="B435" t="s">
         <v>821</v>
@@ -27262,7 +27279,7 @@
     </row>
     <row r="436" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>827</v>
+        <v>820</v>
       </c>
       <c r="B436" t="s">
         <v>821</v>
@@ -27311,8 +27328,8 @@
       </c>
     </row>
     <row r="437" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A437" s="1" t="s">
-        <v>1193</v>
+      <c r="A437" t="s">
+        <v>827</v>
       </c>
       <c r="B437" t="s">
         <v>821</v>
@@ -27361,8 +27378,8 @@
       </c>
     </row>
     <row r="438" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A438" t="s">
-        <v>828</v>
+      <c r="A438" s="1" t="s">
+        <v>1193</v>
       </c>
       <c r="B438" t="s">
         <v>821</v>
@@ -27412,122 +27429,122 @@
     </row>
     <row r="439" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B439" t="s">
-        <v>830</v>
+        <v>821</v>
       </c>
       <c r="C439" t="s">
         <v>17</v>
       </c>
       <c r="D439" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="E439" t="s">
-        <v>19</v>
+        <v>822</v>
       </c>
       <c r="F439" t="s">
-        <v>379</v>
+        <v>823</v>
       </c>
       <c r="G439" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="H439" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
       <c r="I439" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="J439" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K439" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="L439" t="s">
-        <v>383</v>
+        <v>110</v>
       </c>
       <c r="M439">
         <v>1</v>
       </c>
       <c r="N439" t="s">
-        <v>383</v>
+        <v>821</v>
       </c>
       <c r="O439" t="s">
-        <v>26</v>
+        <v>111</v>
       </c>
       <c r="P439" t="s">
-        <v>1338</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="440" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="B440" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="C440" t="s">
         <v>17</v>
       </c>
       <c r="D440" t="s">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="E440" t="s">
-        <v>124</v>
+        <v>19</v>
       </c>
       <c r="F440" t="s">
-        <v>125</v>
-      </c>
-      <c r="G440" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H440" t="e">
-        <v>#N/A</v>
+        <v>379</v>
+      </c>
+      <c r="G440" t="s">
+        <v>831</v>
+      </c>
+      <c r="H440" t="s">
+        <v>832</v>
       </c>
       <c r="I440" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="J440" t="b">
         <v>0</v>
       </c>
       <c r="K440" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="L440" t="s">
-        <v>129</v>
+        <v>383</v>
       </c>
       <c r="M440">
         <v>1</v>
       </c>
       <c r="N440" t="s">
-        <v>129</v>
+        <v>383</v>
       </c>
       <c r="O440" t="s">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="P440" t="s">
-        <v>1311</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="441" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="B441" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="C441" t="s">
         <v>17</v>
       </c>
-      <c r="D441" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E441" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F441" t="e">
-        <v>#N/A</v>
+      <c r="D441" t="s">
+        <v>123</v>
+      </c>
+      <c r="E441" t="s">
+        <v>124</v>
+      </c>
+      <c r="F441" t="s">
+        <v>125</v>
       </c>
       <c r="G441" t="e">
         <v>#N/A</v>
@@ -27536,7 +27553,7 @@
         <v>#N/A</v>
       </c>
       <c r="I441" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="J441" t="b">
         <v>0</v>
@@ -27545,24 +27562,24 @@
         <v>109</v>
       </c>
       <c r="L441" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="M441">
         <v>1</v>
       </c>
       <c r="N441" t="s">
-        <v>838</v>
+        <v>129</v>
       </c>
       <c r="O441" t="s">
-        <v>838</v>
+        <v>95</v>
       </c>
       <c r="P441" t="s">
-        <v>1316</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="442" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B442" t="s">
         <v>838</v>
@@ -27612,7 +27629,7 @@
     </row>
     <row r="443" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B443" t="s">
         <v>838</v>
@@ -27662,7 +27679,7 @@
     </row>
     <row r="444" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>1107</v>
+        <v>840</v>
       </c>
       <c r="B444" t="s">
         <v>838</v>
@@ -27712,7 +27729,7 @@
     </row>
     <row r="445" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>841</v>
+        <v>1107</v>
       </c>
       <c r="B445" t="s">
         <v>838</v>
@@ -27762,7 +27779,7 @@
     </row>
     <row r="446" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B446" t="s">
         <v>838</v>
@@ -27812,7 +27829,7 @@
     </row>
     <row r="447" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B447" t="s">
         <v>838</v>
@@ -27862,7 +27879,7 @@
     </row>
     <row r="448" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>1543</v>
+        <v>843</v>
       </c>
       <c r="B448" t="s">
         <v>838</v>
@@ -27912,7 +27929,7 @@
     </row>
     <row r="449" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>844</v>
+        <v>1543</v>
       </c>
       <c r="B449" t="s">
         <v>838</v>
@@ -27962,7 +27979,7 @@
     </row>
     <row r="450" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>1382</v>
+        <v>844</v>
       </c>
       <c r="B450" t="s">
         <v>838</v>
@@ -28011,8 +28028,8 @@
       </c>
     </row>
     <row r="451" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A451" s="1" t="s">
-        <v>1203</v>
+      <c r="A451" t="s">
+        <v>1382</v>
       </c>
       <c r="B451" t="s">
         <v>838</v>
@@ -28061,8 +28078,8 @@
       </c>
     </row>
     <row r="452" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A452" t="s">
-        <v>845</v>
+      <c r="A452" s="1" t="s">
+        <v>1203</v>
       </c>
       <c r="B452" t="s">
         <v>838</v>
@@ -28112,7 +28129,7 @@
     </row>
     <row r="453" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B453" t="s">
         <v>838</v>
@@ -28162,7 +28179,7 @@
     </row>
     <row r="454" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B454" t="s">
         <v>838</v>
@@ -28211,8 +28228,8 @@
       </c>
     </row>
     <row r="455" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A455" s="1" t="s">
-        <v>1232</v>
+      <c r="A455" t="s">
+        <v>847</v>
       </c>
       <c r="B455" t="s">
         <v>838</v>
@@ -28261,8 +28278,8 @@
       </c>
     </row>
     <row r="456" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A456" t="s">
-        <v>1077</v>
+      <c r="A456" s="1" t="s">
+        <v>1232</v>
       </c>
       <c r="B456" t="s">
         <v>838</v>
@@ -28312,7 +28329,7 @@
     </row>
     <row r="457" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>848</v>
+        <v>1077</v>
       </c>
       <c r="B457" t="s">
         <v>838</v>
@@ -28362,7 +28379,7 @@
     </row>
     <row r="458" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B458" t="s">
         <v>838</v>
@@ -28412,7 +28429,7 @@
     </row>
     <row r="459" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B459" t="s">
         <v>838</v>
@@ -28462,7 +28479,7 @@
     </row>
     <row r="460" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B460" t="s">
         <v>838</v>
@@ -28512,7 +28529,7 @@
     </row>
     <row r="461" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B461" t="s">
         <v>838</v>
@@ -28562,7 +28579,7 @@
     </row>
     <row r="462" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B462" t="s">
         <v>838</v>
@@ -28612,7 +28629,7 @@
     </row>
     <row r="463" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B463" t="s">
         <v>838</v>
@@ -28662,7 +28679,7 @@
     </row>
     <row r="464" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B464" t="s">
         <v>838</v>
@@ -28712,7 +28729,7 @@
     </row>
     <row r="465" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B465" t="s">
         <v>838</v>
@@ -28761,8 +28778,8 @@
       </c>
     </row>
     <row r="466" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A466" s="1" t="s">
-        <v>1218</v>
+      <c r="A466" t="s">
+        <v>856</v>
       </c>
       <c r="B466" t="s">
         <v>838</v>
@@ -28811,8 +28828,8 @@
       </c>
     </row>
     <row r="467" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A467" t="s">
-        <v>857</v>
+      <c r="A467" s="1" t="s">
+        <v>1218</v>
       </c>
       <c r="B467" t="s">
         <v>838</v>
@@ -28862,7 +28879,7 @@
     </row>
     <row r="468" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B468" t="s">
         <v>838</v>
@@ -28912,7 +28929,7 @@
     </row>
     <row r="469" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>1407</v>
+        <v>858</v>
       </c>
       <c r="B469" t="s">
         <v>838</v>
@@ -28962,37 +28979,37 @@
     </row>
     <row r="470" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>1537</v>
+        <v>1407</v>
       </c>
       <c r="B470" t="s">
-        <v>1538</v>
+        <v>838</v>
       </c>
       <c r="C470" t="s">
         <v>17</v>
       </c>
-      <c r="D470" t="s">
-        <v>87</v>
-      </c>
-      <c r="E470" t="s">
-        <v>88</v>
-      </c>
-      <c r="F470" t="s">
-        <v>1489</v>
-      </c>
-      <c r="G470" t="s">
-        <v>1489</v>
-      </c>
-      <c r="H470" t="s">
-        <v>1489</v>
+      <c r="D470" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E470" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F470" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G470" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H470" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I470" t="s">
-        <v>1539</v>
+        <v>838</v>
       </c>
       <c r="J470" t="b">
         <v>0</v>
       </c>
       <c r="K470" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="L470" t="s">
         <v>93</v>
@@ -29001,48 +29018,48 @@
         <v>1</v>
       </c>
       <c r="N470" t="s">
-        <v>94</v>
+        <v>838</v>
       </c>
       <c r="O470" t="s">
-        <v>95</v>
+        <v>838</v>
       </c>
       <c r="P470" t="s">
-        <v>1310</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="471" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>859</v>
+        <v>1537</v>
       </c>
       <c r="B471" t="s">
-        <v>860</v>
+        <v>1538</v>
       </c>
       <c r="C471" t="s">
         <v>17</v>
       </c>
       <c r="D471" t="s">
-        <v>861</v>
+        <v>87</v>
       </c>
       <c r="E471" t="s">
-        <v>862</v>
-      </c>
-      <c r="F471" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G471" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H471" t="e">
-        <v>#N/A</v>
+        <v>88</v>
+      </c>
+      <c r="F471" t="s">
+        <v>1489</v>
+      </c>
+      <c r="G471" t="s">
+        <v>1489</v>
+      </c>
+      <c r="H471" t="s">
+        <v>1489</v>
       </c>
       <c r="I471" t="s">
-        <v>863</v>
+        <v>1539</v>
       </c>
       <c r="J471" t="b">
         <v>0</v>
       </c>
       <c r="K471" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="L471" t="s">
         <v>93</v>
@@ -29051,18 +29068,18 @@
         <v>1</v>
       </c>
       <c r="N471" t="s">
-        <v>864</v>
+        <v>94</v>
       </c>
       <c r="O471" t="s">
         <v>95</v>
       </c>
       <c r="P471" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="472" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="B472" t="s">
         <v>860</v>
@@ -29112,7 +29129,7 @@
     </row>
     <row r="473" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B473" t="s">
         <v>860</v>
@@ -29162,22 +29179,22 @@
     </row>
     <row r="474" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B474" t="s">
-        <v>868</v>
+        <v>860</v>
       </c>
       <c r="C474" t="s">
         <v>17</v>
       </c>
       <c r="D474" t="s">
-        <v>18</v>
+        <v>861</v>
       </c>
       <c r="E474" t="s">
-        <v>869</v>
-      </c>
-      <c r="F474" t="s">
-        <v>870</v>
+        <v>862</v>
+      </c>
+      <c r="F474" t="e">
+        <v>#N/A</v>
       </c>
       <c r="G474" t="e">
         <v>#N/A</v>
@@ -29186,33 +29203,33 @@
         <v>#N/A</v>
       </c>
       <c r="I474" t="s">
-        <v>871</v>
+        <v>863</v>
       </c>
       <c r="J474" t="b">
         <v>0</v>
       </c>
       <c r="K474" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="L474" t="s">
-        <v>871</v>
+        <v>93</v>
       </c>
       <c r="M474">
         <v>1</v>
       </c>
       <c r="N474" t="s">
-        <v>871</v>
+        <v>864</v>
       </c>
       <c r="O474" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="P474" t="s">
-        <v>1329</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="475" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="B475" t="s">
         <v>868</v>
@@ -29262,7 +29279,7 @@
     </row>
     <row r="476" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B476" t="s">
         <v>868</v>
@@ -29312,7 +29329,7 @@
     </row>
     <row r="477" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B477" t="s">
         <v>868</v>
@@ -29362,7 +29379,7 @@
     </row>
     <row r="478" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B478" t="s">
         <v>868</v>
@@ -29412,10 +29429,10 @@
     </row>
     <row r="479" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>1352</v>
+        <v>875</v>
       </c>
       <c r="B479" t="s">
-        <v>876</v>
+        <v>868</v>
       </c>
       <c r="C479" t="s">
         <v>17</v>
@@ -29424,10 +29441,10 @@
         <v>18</v>
       </c>
       <c r="E479" t="s">
-        <v>76</v>
+        <v>869</v>
       </c>
       <c r="F479" t="s">
-        <v>77</v>
+        <v>870</v>
       </c>
       <c r="G479" t="e">
         <v>#N/A</v>
@@ -29436,7 +29453,7 @@
         <v>#N/A</v>
       </c>
       <c r="I479" t="s">
-        <v>877</v>
+        <v>871</v>
       </c>
       <c r="J479" t="b">
         <v>0</v>
@@ -29445,24 +29462,24 @@
         <v>24</v>
       </c>
       <c r="L479" t="s">
-        <v>81</v>
+        <v>871</v>
       </c>
       <c r="M479">
         <v>1</v>
       </c>
       <c r="N479" t="s">
-        <v>81</v>
+        <v>871</v>
       </c>
       <c r="O479" t="s">
         <v>26</v>
       </c>
       <c r="P479" t="s">
-        <v>1339</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="480" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>878</v>
+        <v>1352</v>
       </c>
       <c r="B480" t="s">
         <v>876</v>
@@ -29512,7 +29529,7 @@
     </row>
     <row r="481" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>1098</v>
+        <v>878</v>
       </c>
       <c r="B481" t="s">
         <v>876</v>
@@ -29562,7 +29579,7 @@
     </row>
     <row r="482" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>1106</v>
+        <v>1098</v>
       </c>
       <c r="B482" t="s">
         <v>876</v>
@@ -29612,7 +29629,7 @@
     </row>
     <row r="483" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B483" t="s">
         <v>876</v>
@@ -29662,7 +29679,7 @@
     </row>
     <row r="484" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>879</v>
+        <v>1105</v>
       </c>
       <c r="B484" t="s">
         <v>876</v>
@@ -29712,7 +29729,7 @@
     </row>
     <row r="485" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>1351</v>
+        <v>879</v>
       </c>
       <c r="B485" t="s">
         <v>876</v>
@@ -29762,10 +29779,10 @@
     </row>
     <row r="486" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>880</v>
+        <v>1351</v>
       </c>
       <c r="B486" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="C486" t="s">
         <v>17</v>
@@ -29773,11 +29790,11 @@
       <c r="D486" t="s">
         <v>18</v>
       </c>
-      <c r="E486" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F486" t="e">
-        <v>#N/A</v>
+      <c r="E486" t="s">
+        <v>76</v>
+      </c>
+      <c r="F486" t="s">
+        <v>77</v>
       </c>
       <c r="G486" t="e">
         <v>#N/A</v>
@@ -29786,7 +29803,7 @@
         <v>#N/A</v>
       </c>
       <c r="I486" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="J486" t="b">
         <v>0</v>
@@ -29795,24 +29812,24 @@
         <v>24</v>
       </c>
       <c r="L486" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="M486">
         <v>1</v>
       </c>
       <c r="N486" t="s">
-        <v>883</v>
+        <v>81</v>
       </c>
       <c r="O486" t="s">
         <v>26</v>
       </c>
       <c r="P486" t="s">
-        <v>1305</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="487" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="B487" t="s">
         <v>881</v>
@@ -29861,8 +29878,8 @@
       </c>
     </row>
     <row r="488" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A488" s="1" t="s">
-        <v>1194</v>
+      <c r="A488" t="s">
+        <v>884</v>
       </c>
       <c r="B488" t="s">
         <v>881</v>
@@ -29911,8 +29928,8 @@
       </c>
     </row>
     <row r="489" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A489" t="s">
-        <v>885</v>
+      <c r="A489" s="1" t="s">
+        <v>1194</v>
       </c>
       <c r="B489" t="s">
         <v>881</v>
@@ -29962,7 +29979,7 @@
     </row>
     <row r="490" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B490" t="s">
         <v>881</v>
@@ -30012,7 +30029,7 @@
     </row>
     <row r="491" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B491" t="s">
         <v>881</v>
@@ -30062,7 +30079,7 @@
     </row>
     <row r="492" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B492" t="s">
         <v>881</v>
@@ -30112,7 +30129,7 @@
     </row>
     <row r="493" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B493" t="s">
         <v>881</v>
@@ -30161,8 +30178,8 @@
       </c>
     </row>
     <row r="494" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A494" s="1" t="s">
-        <v>1204</v>
+      <c r="A494" t="s">
+        <v>889</v>
       </c>
       <c r="B494" t="s">
         <v>881</v>
@@ -30211,8 +30228,8 @@
       </c>
     </row>
     <row r="495" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A495" t="s">
-        <v>1119</v>
+      <c r="A495" s="1" t="s">
+        <v>1204</v>
       </c>
       <c r="B495" t="s">
         <v>881</v>
@@ -30262,7 +30279,7 @@
     </row>
     <row r="496" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>1471</v>
+        <v>1119</v>
       </c>
       <c r="B496" t="s">
         <v>881</v>
@@ -30312,7 +30329,7 @@
     </row>
     <row r="497" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="B497" t="s">
         <v>881</v>
@@ -30362,7 +30379,7 @@
     </row>
     <row r="498" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="B498" t="s">
         <v>881</v>
@@ -30412,19 +30429,19 @@
     </row>
     <row r="499" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>890</v>
+        <v>1473</v>
       </c>
       <c r="B499" t="s">
-        <v>891</v>
+        <v>881</v>
       </c>
       <c r="C499" t="s">
         <v>17</v>
       </c>
       <c r="D499" t="s">
-        <v>103</v>
-      </c>
-      <c r="E499" t="s">
-        <v>892</v>
+        <v>18</v>
+      </c>
+      <c r="E499" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F499" t="e">
         <v>#N/A</v>
@@ -30436,7 +30453,7 @@
         <v>#N/A</v>
       </c>
       <c r="I499" t="s">
-        <v>893</v>
+        <v>882</v>
       </c>
       <c r="J499" t="b">
         <v>0</v>
@@ -30445,24 +30462,24 @@
         <v>24</v>
       </c>
       <c r="L499" t="s">
-        <v>894</v>
+        <v>93</v>
       </c>
       <c r="M499">
         <v>1</v>
       </c>
       <c r="N499" t="s">
-        <v>894</v>
+        <v>883</v>
       </c>
       <c r="O499" t="s">
-        <v>339</v>
+        <v>26</v>
       </c>
       <c r="P499" t="s">
-        <v>1299</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="500" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="B500" t="s">
         <v>891</v>
@@ -30512,7 +30529,7 @@
     </row>
     <row r="501" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>1353</v>
+        <v>895</v>
       </c>
       <c r="B501" t="s">
         <v>891</v>
@@ -30561,8 +30578,8 @@
       </c>
     </row>
     <row r="502" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A502" s="1" t="s">
-        <v>1201</v>
+      <c r="A502" t="s">
+        <v>1353</v>
       </c>
       <c r="B502" t="s">
         <v>891</v>
@@ -30611,8 +30628,8 @@
       </c>
     </row>
     <row r="503" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A503" t="s">
-        <v>896</v>
+      <c r="A503" s="1" t="s">
+        <v>1201</v>
       </c>
       <c r="B503" t="s">
         <v>891</v>
@@ -30662,7 +30679,7 @@
     </row>
     <row r="504" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B504" t="s">
         <v>891</v>
@@ -30712,7 +30729,7 @@
     </row>
     <row r="505" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B505" t="s">
         <v>891</v>
@@ -30762,7 +30779,7 @@
     </row>
     <row r="506" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B506" t="s">
         <v>891</v>
@@ -30812,7 +30829,7 @@
     </row>
     <row r="507" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>1083</v>
+        <v>899</v>
       </c>
       <c r="B507" t="s">
         <v>891</v>
@@ -30862,7 +30879,7 @@
     </row>
     <row r="508" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>900</v>
+        <v>1083</v>
       </c>
       <c r="B508" t="s">
         <v>891</v>
@@ -30912,7 +30929,7 @@
     </row>
     <row r="509" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>1361</v>
+        <v>900</v>
       </c>
       <c r="B509" t="s">
         <v>891</v>
@@ -30962,7 +30979,7 @@
     </row>
     <row r="510" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>1075</v>
+        <v>1361</v>
       </c>
       <c r="B510" t="s">
         <v>891</v>
@@ -31012,22 +31029,22 @@
     </row>
     <row r="511" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>913</v>
+        <v>1075</v>
       </c>
       <c r="B511" t="s">
-        <v>914</v>
+        <v>891</v>
       </c>
       <c r="C511" t="s">
         <v>17</v>
       </c>
       <c r="D511" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="E511" t="s">
-        <v>180</v>
-      </c>
-      <c r="F511" t="s">
-        <v>181</v>
+        <v>892</v>
+      </c>
+      <c r="F511" t="e">
+        <v>#N/A</v>
       </c>
       <c r="G511" t="e">
         <v>#N/A</v>
@@ -31036,7 +31053,7 @@
         <v>#N/A</v>
       </c>
       <c r="I511" t="s">
-        <v>915</v>
+        <v>893</v>
       </c>
       <c r="J511" t="b">
         <v>0</v>
@@ -31045,24 +31062,24 @@
         <v>24</v>
       </c>
       <c r="L511" t="s">
-        <v>185</v>
+        <v>894</v>
       </c>
       <c r="M511">
         <v>1</v>
       </c>
       <c r="N511" t="s">
-        <v>185</v>
+        <v>894</v>
       </c>
       <c r="O511" t="s">
-        <v>26</v>
+        <v>339</v>
       </c>
       <c r="P511" t="s">
-        <v>1333</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="512" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>1120</v>
+        <v>913</v>
       </c>
       <c r="B512" t="s">
         <v>914</v>
@@ -31112,22 +31129,22 @@
     </row>
     <row r="513" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>916</v>
+        <v>1120</v>
       </c>
       <c r="B513" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="C513" t="s">
         <v>17</v>
       </c>
       <c r="D513" t="s">
-        <v>918</v>
+        <v>18</v>
       </c>
       <c r="E513" t="s">
-        <v>919</v>
-      </c>
-      <c r="F513" t="e">
-        <v>#N/A</v>
+        <v>180</v>
+      </c>
+      <c r="F513" t="s">
+        <v>181</v>
       </c>
       <c r="G513" t="e">
         <v>#N/A</v>
@@ -31136,48 +31153,48 @@
         <v>#N/A</v>
       </c>
       <c r="I513" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="J513" t="b">
         <v>0</v>
       </c>
       <c r="K513" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="L513" t="s">
-        <v>93</v>
+        <v>185</v>
       </c>
       <c r="M513">
         <v>1</v>
       </c>
       <c r="N513" t="s">
-        <v>920</v>
+        <v>185</v>
       </c>
       <c r="O513" t="s">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="P513" t="s">
-        <v>1309</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="514" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="B514" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="C514" t="s">
         <v>17</v>
       </c>
       <c r="D514" t="s">
-        <v>103</v>
+        <v>918</v>
       </c>
       <c r="E514" t="s">
-        <v>132</v>
-      </c>
-      <c r="F514" t="s">
-        <v>326</v>
+        <v>919</v>
+      </c>
+      <c r="F514" t="e">
+        <v>#N/A</v>
       </c>
       <c r="G514" t="e">
         <v>#N/A</v>
@@ -31186,7 +31203,7 @@
         <v>#N/A</v>
       </c>
       <c r="I514" t="s">
-        <v>330</v>
+        <v>920</v>
       </c>
       <c r="J514" t="b">
         <v>0</v>
@@ -31195,24 +31212,24 @@
         <v>109</v>
       </c>
       <c r="L514" t="s">
-        <v>330</v>
+        <v>93</v>
       </c>
       <c r="M514">
         <v>1</v>
       </c>
       <c r="N514" t="s">
-        <v>330</v>
+        <v>920</v>
       </c>
       <c r="O514" t="s">
-        <v>331</v>
+        <v>95</v>
       </c>
       <c r="P514" t="s">
-        <v>1303</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="515" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B515" t="s">
         <v>922</v>
@@ -31262,7 +31279,7 @@
     </row>
     <row r="516" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B516" t="s">
         <v>922</v>
@@ -31311,11 +31328,11 @@
       </c>
     </row>
     <row r="517" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A517" s="1" t="s">
-        <v>1158</v>
+      <c r="A517" t="s">
+        <v>924</v>
       </c>
       <c r="B517" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="C517" t="s">
         <v>17</v>
@@ -31324,10 +31341,10 @@
         <v>103</v>
       </c>
       <c r="E517" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="F517" t="s">
-        <v>105</v>
+        <v>326</v>
       </c>
       <c r="G517" t="e">
         <v>#N/A</v>
@@ -31336,33 +31353,33 @@
         <v>#N/A</v>
       </c>
       <c r="I517" t="s">
-        <v>927</v>
+        <v>330</v>
       </c>
       <c r="J517" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K517" t="s">
         <v>109</v>
       </c>
       <c r="L517" t="s">
-        <v>928</v>
+        <v>330</v>
       </c>
       <c r="M517">
         <v>1</v>
       </c>
       <c r="N517" t="s">
-        <v>928</v>
+        <v>330</v>
       </c>
       <c r="O517" t="s">
-        <v>111</v>
+        <v>331</v>
       </c>
       <c r="P517" t="s">
-        <v>1322</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="518" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A518" t="s">
-        <v>925</v>
+      <c r="A518" s="1" t="s">
+        <v>1158</v>
       </c>
       <c r="B518" t="s">
         <v>926</v>
@@ -31411,8 +31428,8 @@
       </c>
     </row>
     <row r="519" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A519" s="1" t="s">
-        <v>1202</v>
+      <c r="A519" t="s">
+        <v>925</v>
       </c>
       <c r="B519" t="s">
         <v>926</v>
@@ -31462,7 +31479,7 @@
     </row>
     <row r="520" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
       <c r="B520" t="s">
         <v>926</v>
@@ -31512,7 +31529,7 @@
     </row>
     <row r="521" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B521" t="s">
         <v>926</v>
@@ -31562,7 +31579,7 @@
     </row>
     <row r="522" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="s">
-        <v>1349</v>
+        <v>1208</v>
       </c>
       <c r="B522" t="s">
         <v>926</v>
@@ -31612,7 +31629,7 @@
     </row>
     <row r="523" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
-        <v>1209</v>
+        <v>1349</v>
       </c>
       <c r="B523" t="s">
         <v>926</v>
@@ -31661,8 +31678,8 @@
       </c>
     </row>
     <row r="524" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A524" t="s">
-        <v>929</v>
+      <c r="A524" s="1" t="s">
+        <v>1209</v>
       </c>
       <c r="B524" t="s">
         <v>926</v>
@@ -31712,22 +31729,22 @@
     </row>
     <row r="525" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B525" t="s">
-        <v>931</v>
+        <v>926</v>
       </c>
       <c r="C525" t="s">
         <v>17</v>
       </c>
       <c r="D525" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="E525" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="F525" t="s">
-        <v>932</v>
+        <v>105</v>
       </c>
       <c r="G525" t="e">
         <v>#N/A</v>
@@ -31736,33 +31753,33 @@
         <v>#N/A</v>
       </c>
       <c r="I525" t="s">
-        <v>933</v>
+        <v>927</v>
       </c>
       <c r="J525" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K525" t="s">
         <v>109</v>
       </c>
       <c r="L525" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
       <c r="M525">
         <v>1</v>
       </c>
       <c r="N525" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
       <c r="O525" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="P525" t="s">
-        <v>1312</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="526" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A526" s="1" t="s">
-        <v>1159</v>
+      <c r="A526" t="s">
+        <v>930</v>
       </c>
       <c r="B526" t="s">
         <v>931</v>
@@ -31812,7 +31829,7 @@
     </row>
     <row r="527" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
-        <v>1210</v>
+        <v>1159</v>
       </c>
       <c r="B527" t="s">
         <v>931</v>
@@ -31861,8 +31878,8 @@
       </c>
     </row>
     <row r="528" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A528" t="s">
-        <v>935</v>
+      <c r="A528" s="1" t="s">
+        <v>1210</v>
       </c>
       <c r="B528" t="s">
         <v>931</v>
@@ -31912,22 +31929,22 @@
     </row>
     <row r="529" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>1100</v>
+        <v>935</v>
       </c>
       <c r="B529" t="s">
-        <v>1101</v>
+        <v>931</v>
       </c>
       <c r="C529" t="s">
         <v>17</v>
       </c>
       <c r="D529" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="E529" t="s">
-        <v>1102</v>
-      </c>
-      <c r="F529" t="e">
-        <v>#N/A</v>
+        <v>124</v>
+      </c>
+      <c r="F529" t="s">
+        <v>932</v>
       </c>
       <c r="G529" t="e">
         <v>#N/A</v>
@@ -31936,33 +31953,33 @@
         <v>#N/A</v>
       </c>
       <c r="I529" t="s">
-        <v>1103</v>
+        <v>933</v>
       </c>
       <c r="J529" t="b">
         <v>0</v>
       </c>
       <c r="K529" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="L529" t="s">
-        <v>93</v>
+        <v>934</v>
       </c>
       <c r="M529">
         <v>1</v>
       </c>
       <c r="N529" t="s">
-        <v>94</v>
+        <v>934</v>
       </c>
       <c r="O529" t="s">
         <v>95</v>
       </c>
       <c r="P529" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="530" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
       <c r="B530" t="s">
         <v>1101</v>
@@ -32011,8 +32028,8 @@
       </c>
     </row>
     <row r="531" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A531" s="1" t="s">
-        <v>1221</v>
+      <c r="A531" t="s">
+        <v>1104</v>
       </c>
       <c r="B531" t="s">
         <v>1101</v>
@@ -32061,11 +32078,11 @@
       </c>
     </row>
     <row r="532" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A532" t="s">
-        <v>936</v>
+      <c r="A532" s="1" t="s">
+        <v>1221</v>
       </c>
       <c r="B532" t="s">
-        <v>937</v>
+        <v>1101</v>
       </c>
       <c r="C532" t="s">
         <v>17</v>
@@ -32074,7 +32091,7 @@
         <v>87</v>
       </c>
       <c r="E532" t="s">
-        <v>296</v>
+        <v>1102</v>
       </c>
       <c r="F532" t="e">
         <v>#N/A</v>
@@ -32086,7 +32103,7 @@
         <v>#N/A</v>
       </c>
       <c r="I532" t="s">
-        <v>938</v>
+        <v>1103</v>
       </c>
       <c r="J532" t="b">
         <v>0</v>
@@ -32112,10 +32129,10 @@
     </row>
     <row r="533" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>1597</v>
+        <v>936</v>
       </c>
       <c r="B533" t="s">
-        <v>1595</v>
+        <v>937</v>
       </c>
       <c r="C533" t="s">
         <v>17</v>
@@ -32123,8 +32140,8 @@
       <c r="D533" t="s">
         <v>87</v>
       </c>
-      <c r="E533" t="e">
-        <v>#N/A</v>
+      <c r="E533" t="s">
+        <v>296</v>
       </c>
       <c r="F533" t="e">
         <v>#N/A</v>
@@ -32136,7 +32153,7 @@
         <v>#N/A</v>
       </c>
       <c r="I533" t="s">
-        <v>1596</v>
+        <v>938</v>
       </c>
       <c r="J533" t="b">
         <v>0</v>
@@ -32162,7 +32179,7 @@
     </row>
     <row r="534" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>1594</v>
+        <v>1597</v>
       </c>
       <c r="B534" t="s">
         <v>1595</v>
@@ -32212,22 +32229,22 @@
     </row>
     <row r="535" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>1531</v>
+        <v>1594</v>
       </c>
       <c r="B535" t="s">
-        <v>1427</v>
+        <v>1595</v>
       </c>
       <c r="C535" t="s">
         <v>17</v>
       </c>
       <c r="D535" t="s">
-        <v>103</v>
-      </c>
-      <c r="E535" t="s">
-        <v>104</v>
-      </c>
-      <c r="F535" t="s">
-        <v>704</v>
+        <v>87</v>
+      </c>
+      <c r="E535" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F535" t="e">
+        <v>#N/A</v>
       </c>
       <c r="G535" t="e">
         <v>#N/A</v>
@@ -32236,33 +32253,33 @@
         <v>#N/A</v>
       </c>
       <c r="I535" t="s">
-        <v>1427</v>
+        <v>1596</v>
       </c>
       <c r="J535" t="b">
         <v>0</v>
       </c>
       <c r="K535" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="L535" t="s">
-        <v>708</v>
+        <v>93</v>
       </c>
       <c r="M535">
         <v>1</v>
       </c>
       <c r="N535" t="s">
-        <v>708</v>
+        <v>94</v>
       </c>
       <c r="O535" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="P535" t="s">
-        <v>1325</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="536" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B536" t="s">
         <v>1427</v>
@@ -32311,8 +32328,8 @@
       </c>
     </row>
     <row r="537" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A537" s="1" t="s">
-        <v>1173</v>
+      <c r="A537" t="s">
+        <v>1532</v>
       </c>
       <c r="B537" t="s">
         <v>1427</v>
@@ -32362,7 +32379,7 @@
     </row>
     <row r="538" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="s">
-        <v>1181</v>
+        <v>1173</v>
       </c>
       <c r="B538" t="s">
         <v>1427</v>
@@ -32411,8 +32428,8 @@
       </c>
     </row>
     <row r="539" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A539" t="s">
-        <v>709</v>
+      <c r="A539" s="1" t="s">
+        <v>1181</v>
       </c>
       <c r="B539" t="s">
         <v>1427</v>
@@ -32462,7 +32479,7 @@
     </row>
     <row r="540" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B540" t="s">
         <v>1427</v>
@@ -32512,7 +32529,7 @@
     </row>
     <row r="541" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B541" t="s">
         <v>1427</v>
@@ -32561,8 +32578,8 @@
       </c>
     </row>
     <row r="542" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A542" s="1" t="s">
-        <v>1195</v>
+      <c r="A542" t="s">
+        <v>712</v>
       </c>
       <c r="B542" t="s">
         <v>1427</v>
@@ -32612,7 +32629,7 @@
     </row>
     <row r="543" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="B543" t="s">
         <v>1427</v>
@@ -32662,7 +32679,7 @@
     </row>
     <row r="544" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="B544" t="s">
         <v>1427</v>
@@ -32712,7 +32729,7 @@
     </row>
     <row r="545" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
-        <v>1426</v>
+        <v>1197</v>
       </c>
       <c r="B545" t="s">
         <v>1427</v>
@@ -32761,8 +32778,8 @@
       </c>
     </row>
     <row r="546" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A546" t="s">
-        <v>713</v>
+      <c r="A546" s="1" t="s">
+        <v>1426</v>
       </c>
       <c r="B546" t="s">
         <v>1427</v>
@@ -32812,7 +32829,7 @@
     </row>
     <row r="547" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B547" t="s">
         <v>1427</v>
@@ -32862,7 +32879,7 @@
     </row>
     <row r="548" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B548" t="s">
         <v>1427</v>
@@ -32912,7 +32929,7 @@
     </row>
     <row r="549" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B549" t="s">
         <v>1427</v>
@@ -32961,8 +32978,8 @@
       </c>
     </row>
     <row r="550" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A550" s="1" t="s">
-        <v>1212</v>
+      <c r="A550" t="s">
+        <v>716</v>
       </c>
       <c r="B550" t="s">
         <v>1427</v>
@@ -33011,8 +33028,8 @@
       </c>
     </row>
     <row r="551" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A551" t="s">
-        <v>717</v>
+      <c r="A551" s="1" t="s">
+        <v>1212</v>
       </c>
       <c r="B551" t="s">
         <v>1427</v>
@@ -33061,8 +33078,8 @@
       </c>
     </row>
     <row r="552" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A552" s="1" t="s">
-        <v>1282</v>
+      <c r="A552" t="s">
+        <v>717</v>
       </c>
       <c r="B552" t="s">
         <v>1427</v>
@@ -33112,7 +33129,7 @@
     </row>
     <row r="553" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
-        <v>1432</v>
+        <v>1282</v>
       </c>
       <c r="B553" t="s">
         <v>1427</v>
@@ -33161,8 +33178,8 @@
       </c>
     </row>
     <row r="554" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A554" t="s">
-        <v>718</v>
+      <c r="A554" s="1" t="s">
+        <v>1432</v>
       </c>
       <c r="B554" t="s">
         <v>1427</v>
@@ -33212,10 +33229,10 @@
     </row>
     <row r="555" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>939</v>
+        <v>718</v>
       </c>
       <c r="B555" t="s">
-        <v>940</v>
+        <v>1427</v>
       </c>
       <c r="C555" t="s">
         <v>17</v>
@@ -33224,10 +33241,10 @@
         <v>103</v>
       </c>
       <c r="E555" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="F555" t="s">
-        <v>468</v>
+        <v>704</v>
       </c>
       <c r="G555" t="e">
         <v>#N/A</v>
@@ -33236,33 +33253,33 @@
         <v>#N/A</v>
       </c>
       <c r="I555" t="s">
-        <v>941</v>
+        <v>1427</v>
       </c>
       <c r="J555" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K555" t="s">
         <v>109</v>
       </c>
       <c r="L555" t="s">
-        <v>472</v>
+        <v>708</v>
       </c>
       <c r="M555">
         <v>1</v>
       </c>
       <c r="N555" t="s">
-        <v>472</v>
+        <v>708</v>
       </c>
       <c r="O555" t="s">
-        <v>472</v>
+        <v>111</v>
       </c>
       <c r="P555" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="556" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="B556" t="s">
         <v>940</v>
@@ -33312,22 +33329,22 @@
     </row>
     <row r="557" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B557" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="C557" t="s">
         <v>17</v>
       </c>
       <c r="D557" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="E557" t="s">
-        <v>19</v>
+        <v>132</v>
       </c>
       <c r="F557" t="s">
-        <v>59</v>
+        <v>468</v>
       </c>
       <c r="G557" t="e">
         <v>#N/A</v>
@@ -33336,33 +33353,33 @@
         <v>#N/A</v>
       </c>
       <c r="I557" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="J557" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K557" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="L557" t="s">
-        <v>63</v>
+        <v>472</v>
       </c>
       <c r="M557">
         <v>1</v>
       </c>
       <c r="N557" t="s">
-        <v>63</v>
+        <v>472</v>
       </c>
       <c r="O557" t="s">
-        <v>26</v>
+        <v>472</v>
       </c>
       <c r="P557" t="s">
-        <v>1338</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="558" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="B558" t="s">
         <v>944</v>
@@ -33411,8 +33428,8 @@
       </c>
     </row>
     <row r="559" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A559" s="1" t="s">
-        <v>1280</v>
+      <c r="A559" t="s">
+        <v>946</v>
       </c>
       <c r="B559" t="s">
         <v>944</v>
@@ -33462,7 +33479,7 @@
     </row>
     <row r="560" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
-        <v>1217</v>
+        <v>1280</v>
       </c>
       <c r="B560" t="s">
         <v>944</v>
@@ -33511,11 +33528,11 @@
       </c>
     </row>
     <row r="561" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A561" t="s">
-        <v>1406</v>
+      <c r="A561" s="1" t="s">
+        <v>1217</v>
       </c>
       <c r="B561" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="C561" t="s">
         <v>17</v>
@@ -33524,10 +33541,10 @@
         <v>18</v>
       </c>
       <c r="E561" t="s">
-        <v>279</v>
+        <v>19</v>
       </c>
       <c r="F561" t="s">
-        <v>280</v>
+        <v>59</v>
       </c>
       <c r="G561" t="e">
         <v>#N/A</v>
@@ -33536,7 +33553,7 @@
         <v>#N/A</v>
       </c>
       <c r="I561" t="s">
-        <v>284</v>
+        <v>945</v>
       </c>
       <c r="J561" t="b">
         <v>0</v>
@@ -33545,24 +33562,24 @@
         <v>24</v>
       </c>
       <c r="L561" t="s">
-        <v>284</v>
+        <v>63</v>
       </c>
       <c r="M561">
         <v>1</v>
       </c>
       <c r="N561" t="s">
-        <v>284</v>
+        <v>63</v>
       </c>
       <c r="O561" t="s">
         <v>26</v>
       </c>
       <c r="P561" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="562" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>947</v>
+        <v>1406</v>
       </c>
       <c r="B562" t="s">
         <v>948</v>
@@ -33612,22 +33629,22 @@
     </row>
     <row r="563" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>907</v>
+        <v>947</v>
       </c>
       <c r="B563" t="s">
-        <v>908</v>
+        <v>948</v>
       </c>
       <c r="C563" t="s">
         <v>17</v>
       </c>
       <c r="D563" t="s">
-        <v>103</v>
+        <v>18</v>
       </c>
       <c r="E563" t="s">
-        <v>892</v>
+        <v>279</v>
       </c>
       <c r="F563" t="s">
-        <v>903</v>
+        <v>280</v>
       </c>
       <c r="G563" t="e">
         <v>#N/A</v>
@@ -33636,7 +33653,7 @@
         <v>#N/A</v>
       </c>
       <c r="I563" t="s">
-        <v>909</v>
+        <v>284</v>
       </c>
       <c r="J563" t="b">
         <v>0</v>
@@ -33645,24 +33662,24 @@
         <v>24</v>
       </c>
       <c r="L563" t="s">
-        <v>894</v>
+        <v>284</v>
       </c>
       <c r="M563">
         <v>1</v>
       </c>
       <c r="N563" t="s">
-        <v>894</v>
+        <v>284</v>
       </c>
       <c r="O563" t="s">
-        <v>339</v>
+        <v>26</v>
       </c>
       <c r="P563" t="s">
-        <v>1299</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="564" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>1343</v>
+        <v>907</v>
       </c>
       <c r="B564" t="s">
         <v>908</v>
@@ -33712,7 +33729,7 @@
     </row>
     <row r="565" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>910</v>
+        <v>1343</v>
       </c>
       <c r="B565" t="s">
         <v>908</v>
@@ -33762,7 +33779,7 @@
     </row>
     <row r="566" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B566" t="s">
         <v>908</v>
@@ -33812,7 +33829,7 @@
     </row>
     <row r="567" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B567" t="s">
         <v>908</v>
@@ -33862,22 +33879,22 @@
     </row>
     <row r="568" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>949</v>
+        <v>912</v>
       </c>
       <c r="B568" t="s">
-        <v>950</v>
+        <v>908</v>
       </c>
       <c r="C568" t="s">
         <v>17</v>
       </c>
       <c r="D568" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="E568" t="s">
-        <v>49</v>
+        <v>892</v>
       </c>
       <c r="F568" t="s">
-        <v>50</v>
+        <v>903</v>
       </c>
       <c r="G568" t="e">
         <v>#N/A</v>
@@ -33886,7 +33903,7 @@
         <v>#N/A</v>
       </c>
       <c r="I568" t="s">
-        <v>54</v>
+        <v>909</v>
       </c>
       <c r="J568" t="b">
         <v>0</v>
@@ -33895,24 +33912,24 @@
         <v>24</v>
       </c>
       <c r="L568" t="s">
-        <v>54</v>
+        <v>894</v>
       </c>
       <c r="M568">
         <v>1</v>
       </c>
       <c r="N568" t="s">
-        <v>54</v>
+        <v>894</v>
       </c>
       <c r="O568" t="s">
-        <v>26</v>
+        <v>339</v>
       </c>
       <c r="P568" t="s">
-        <v>1336</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="569" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>1559</v>
+        <v>949</v>
       </c>
       <c r="B569" t="s">
         <v>950</v>
@@ -33961,8 +33978,8 @@
       </c>
     </row>
     <row r="570" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A570" s="1" t="s">
-        <v>1206</v>
+      <c r="A570" t="s">
+        <v>1559</v>
       </c>
       <c r="B570" t="s">
         <v>950</v>
@@ -34011,8 +34028,8 @@
       </c>
     </row>
     <row r="571" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A571" t="s">
-        <v>951</v>
+      <c r="A571" s="1" t="s">
+        <v>1206</v>
       </c>
       <c r="B571" t="s">
         <v>950</v>
@@ -34062,22 +34079,22 @@
     </row>
     <row r="572" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B572" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="C572" t="s">
         <v>17</v>
       </c>
       <c r="D572" t="s">
-        <v>123</v>
-      </c>
-      <c r="E572" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F572" t="e">
-        <v>#N/A</v>
+        <v>18</v>
+      </c>
+      <c r="E572" t="s">
+        <v>49</v>
+      </c>
+      <c r="F572" t="s">
+        <v>50</v>
       </c>
       <c r="G572" t="e">
         <v>#N/A</v>
@@ -34086,33 +34103,33 @@
         <v>#N/A</v>
       </c>
       <c r="I572" t="s">
-        <v>954</v>
+        <v>54</v>
       </c>
       <c r="J572" t="b">
         <v>0</v>
       </c>
       <c r="K572" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="L572" t="s">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="M572">
         <v>1</v>
       </c>
       <c r="N572" t="s">
-        <v>954</v>
+        <v>54</v>
       </c>
       <c r="O572" t="s">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="P572" t="s">
-        <v>1314</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="573" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="B573" t="s">
         <v>953</v>
@@ -34162,10 +34179,10 @@
     </row>
     <row r="574" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B574" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="C574" t="s">
         <v>17</v>
@@ -34173,11 +34190,11 @@
       <c r="D574" t="s">
         <v>123</v>
       </c>
-      <c r="E574" t="s">
-        <v>124</v>
-      </c>
-      <c r="F574" t="s">
-        <v>302</v>
+      <c r="E574" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F574" t="e">
+        <v>#N/A</v>
       </c>
       <c r="G574" t="e">
         <v>#N/A</v>
@@ -34186,7 +34203,7 @@
         <v>#N/A</v>
       </c>
       <c r="I574" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="J574" t="b">
         <v>0</v>
@@ -34195,24 +34212,24 @@
         <v>109</v>
       </c>
       <c r="L574" t="s">
-        <v>306</v>
+        <v>93</v>
       </c>
       <c r="M574">
         <v>1</v>
       </c>
       <c r="N574" t="s">
-        <v>306</v>
+        <v>954</v>
       </c>
       <c r="O574" t="s">
         <v>95</v>
       </c>
       <c r="P574" t="s">
-        <v>1321</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="575" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="B575" t="s">
         <v>957</v>
@@ -34262,7 +34279,7 @@
     </row>
     <row r="576" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B576" t="s">
         <v>957</v>
@@ -34312,7 +34329,7 @@
     </row>
     <row r="577" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B577" t="s">
         <v>957</v>
@@ -34362,7 +34379,7 @@
     </row>
     <row r="578" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B578" t="s">
         <v>957</v>
@@ -34412,7 +34429,7 @@
     </row>
     <row r="579" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B579" t="s">
         <v>957</v>
@@ -34462,7 +34479,7 @@
     </row>
     <row r="580" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B580" t="s">
         <v>957</v>
@@ -34511,8 +34528,8 @@
       </c>
     </row>
     <row r="581" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A581" s="1" t="s">
-        <v>1213</v>
+      <c r="A581" t="s">
+        <v>964</v>
       </c>
       <c r="B581" t="s">
         <v>957</v>
@@ -34562,10 +34579,10 @@
     </row>
     <row r="582" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A582" s="1" t="s">
-        <v>1198</v>
+        <v>1213</v>
       </c>
       <c r="B582" t="s">
-        <v>966</v>
+        <v>957</v>
       </c>
       <c r="C582" t="s">
         <v>17</v>
@@ -34576,8 +34593,8 @@
       <c r="E582" t="s">
         <v>124</v>
       </c>
-      <c r="F582" t="e">
-        <v>#N/A</v>
+      <c r="F582" t="s">
+        <v>302</v>
       </c>
       <c r="G582" t="e">
         <v>#N/A</v>
@@ -34586,7 +34603,7 @@
         <v>#N/A</v>
       </c>
       <c r="I582" t="s">
-        <v>967</v>
+        <v>958</v>
       </c>
       <c r="J582" t="b">
         <v>0</v>
@@ -34595,24 +34612,24 @@
         <v>109</v>
       </c>
       <c r="L582" t="s">
-        <v>194</v>
+        <v>306</v>
       </c>
       <c r="M582">
         <v>1</v>
       </c>
       <c r="N582" t="s">
-        <v>194</v>
+        <v>306</v>
       </c>
       <c r="O582" t="s">
         <v>95</v>
       </c>
       <c r="P582" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="583" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A583" t="s">
-        <v>965</v>
+      <c r="A583" s="1" t="s">
+        <v>1198</v>
       </c>
       <c r="B583" t="s">
         <v>966</v>
@@ -34661,23 +34678,23 @@
       </c>
     </row>
     <row r="584" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A584" s="1" t="s">
-        <v>1214</v>
+      <c r="A584" t="s">
+        <v>965</v>
       </c>
       <c r="B584" t="s">
-        <v>1274</v>
+        <v>966</v>
       </c>
       <c r="C584" t="s">
         <v>17</v>
       </c>
       <c r="D584" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="E584" t="s">
-        <v>764</v>
-      </c>
-      <c r="F584" t="s">
-        <v>765</v>
+        <v>124</v>
+      </c>
+      <c r="F584" t="e">
+        <v>#N/A</v>
       </c>
       <c r="G584" t="e">
         <v>#N/A</v>
@@ -34686,48 +34703,48 @@
         <v>#N/A</v>
       </c>
       <c r="I584" t="s">
-        <v>974</v>
+        <v>967</v>
       </c>
       <c r="J584" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K584" t="s">
         <v>109</v>
       </c>
       <c r="L584" t="s">
-        <v>110</v>
+        <v>194</v>
       </c>
       <c r="M584">
         <v>1</v>
       </c>
       <c r="N584" t="s">
-        <v>973</v>
+        <v>194</v>
       </c>
       <c r="O584" t="s">
-        <v>973</v>
+        <v>95</v>
       </c>
       <c r="P584" t="s">
-        <v>1315</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="585" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A585" t="s">
-        <v>968</v>
+      <c r="A585" s="1" t="s">
+        <v>1214</v>
       </c>
       <c r="B585" t="s">
-        <v>969</v>
+        <v>1274</v>
       </c>
       <c r="C585" t="s">
         <v>17</v>
       </c>
       <c r="D585" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="E585" t="s">
-        <v>124</v>
-      </c>
-      <c r="F585" t="e">
-        <v>#N/A</v>
+        <v>764</v>
+      </c>
+      <c r="F585" t="s">
+        <v>765</v>
       </c>
       <c r="G585" t="e">
         <v>#N/A</v>
@@ -34736,33 +34753,33 @@
         <v>#N/A</v>
       </c>
       <c r="I585" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="J585" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K585" t="s">
         <v>109</v>
       </c>
       <c r="L585" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="M585">
         <v>1</v>
       </c>
       <c r="N585" t="s">
-        <v>954</v>
+        <v>973</v>
       </c>
       <c r="O585" t="s">
-        <v>95</v>
+        <v>973</v>
       </c>
       <c r="P585" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="586" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="B586" t="s">
         <v>969</v>
@@ -34812,19 +34829,19 @@
     </row>
     <row r="587" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>1383</v>
+        <v>971</v>
       </c>
       <c r="B587" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="C587" t="s">
         <v>17</v>
       </c>
       <c r="D587" t="s">
-        <v>103</v>
-      </c>
-      <c r="E587" t="e">
-        <v>#N/A</v>
+        <v>123</v>
+      </c>
+      <c r="E587" t="s">
+        <v>124</v>
       </c>
       <c r="F587" t="e">
         <v>#N/A</v>
@@ -34836,7 +34853,7 @@
         <v>#N/A</v>
       </c>
       <c r="I587" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="J587" t="b">
         <v>0</v>
@@ -34845,24 +34862,24 @@
         <v>109</v>
       </c>
       <c r="L587" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="M587">
         <v>1</v>
       </c>
       <c r="N587" t="s">
-        <v>973</v>
+        <v>954</v>
       </c>
       <c r="O587" t="s">
-        <v>973</v>
+        <v>95</v>
       </c>
       <c r="P587" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="588" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A588" s="1" t="s">
-        <v>1189</v>
+      <c r="A588" t="s">
+        <v>1383</v>
       </c>
       <c r="B588" t="s">
         <v>973</v>
@@ -34911,8 +34928,8 @@
       </c>
     </row>
     <row r="589" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A589" t="s">
-        <v>972</v>
+      <c r="A589" s="1" t="s">
+        <v>1189</v>
       </c>
       <c r="B589" t="s">
         <v>973</v>
@@ -34962,7 +34979,7 @@
     </row>
     <row r="590" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="B590" t="s">
         <v>973</v>
@@ -35012,7 +35029,7 @@
     </row>
     <row r="591" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B591" t="s">
         <v>973</v>
@@ -35061,8 +35078,8 @@
       </c>
     </row>
     <row r="592" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A592" s="1" t="s">
-        <v>1190</v>
+      <c r="A592" t="s">
+        <v>976</v>
       </c>
       <c r="B592" t="s">
         <v>973</v>
@@ -35111,8 +35128,8 @@
       </c>
     </row>
     <row r="593" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A593" t="s">
-        <v>977</v>
+      <c r="A593" s="1" t="s">
+        <v>1190</v>
       </c>
       <c r="B593" t="s">
         <v>973</v>
@@ -35162,7 +35179,7 @@
     </row>
     <row r="594" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B594" t="s">
         <v>973</v>
@@ -35211,8 +35228,8 @@
       </c>
     </row>
     <row r="595" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A595" s="1" t="s">
-        <v>1231</v>
+      <c r="A595" t="s">
+        <v>978</v>
       </c>
       <c r="B595" t="s">
         <v>973</v>
@@ -35261,8 +35278,8 @@
       </c>
     </row>
     <row r="596" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A596" t="s">
-        <v>979</v>
+      <c r="A596" s="1" t="s">
+        <v>1231</v>
       </c>
       <c r="B596" t="s">
         <v>973</v>
@@ -35312,7 +35329,7 @@
     </row>
     <row r="597" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B597" t="s">
         <v>973</v>
@@ -35362,7 +35379,7 @@
     </row>
     <row r="598" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B598" t="s">
         <v>973</v>
@@ -35411,8 +35428,8 @@
       </c>
     </row>
     <row r="599" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A599" s="1" t="s">
-        <v>1199</v>
+      <c r="A599" t="s">
+        <v>981</v>
       </c>
       <c r="B599" t="s">
         <v>973</v>
@@ -35461,8 +35478,8 @@
       </c>
     </row>
     <row r="600" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A600" t="s">
-        <v>982</v>
+      <c r="A600" s="1" t="s">
+        <v>1199</v>
       </c>
       <c r="B600" t="s">
         <v>973</v>
@@ -35512,7 +35529,7 @@
     </row>
     <row r="601" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
-        <v>1425</v>
+        <v>982</v>
       </c>
       <c r="B601" t="s">
         <v>973</v>
@@ -35562,7 +35579,7 @@
     </row>
     <row r="602" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
-        <v>983</v>
+        <v>1425</v>
       </c>
       <c r="B602" t="s">
         <v>973</v>
@@ -35612,7 +35629,7 @@
     </row>
     <row r="603" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B603" t="s">
         <v>973</v>
@@ -35662,7 +35679,7 @@
     </row>
     <row r="604" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B604" t="s">
         <v>973</v>
@@ -35712,7 +35729,7 @@
     </row>
     <row r="605" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B605" t="s">
         <v>973</v>
@@ -35762,7 +35779,7 @@
     </row>
     <row r="606" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B606" t="s">
         <v>973</v>
@@ -35812,7 +35829,7 @@
     </row>
     <row r="607" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B607" t="s">
         <v>973</v>
@@ -35862,7 +35879,7 @@
     </row>
     <row r="608" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
-        <v>1418</v>
+        <v>988</v>
       </c>
       <c r="B608" t="s">
         <v>973</v>
@@ -35912,7 +35929,7 @@
     </row>
     <row r="609" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
-        <v>989</v>
+        <v>1418</v>
       </c>
       <c r="B609" t="s">
         <v>973</v>
@@ -35962,7 +35979,7 @@
     </row>
     <row r="610" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B610" t="s">
         <v>973</v>
@@ -36012,7 +36029,7 @@
     </row>
     <row r="611" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B611" t="s">
         <v>973</v>
@@ -36062,7 +36079,7 @@
     </row>
     <row r="612" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B612" t="s">
         <v>973</v>
@@ -36112,7 +36129,7 @@
     </row>
     <row r="613" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B613" t="s">
         <v>973</v>
@@ -36162,7 +36179,7 @@
     </row>
     <row r="614" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B614" t="s">
         <v>973</v>
@@ -36212,7 +36229,7 @@
     </row>
     <row r="615" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B615" t="s">
         <v>973</v>
@@ -36261,8 +36278,8 @@
       </c>
     </row>
     <row r="616" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A616" s="1" t="s">
-        <v>1215</v>
+      <c r="A616" t="s">
+        <v>995</v>
       </c>
       <c r="B616" t="s">
         <v>973</v>
@@ -36311,8 +36328,8 @@
       </c>
     </row>
     <row r="617" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A617" t="s">
-        <v>996</v>
+      <c r="A617" s="1" t="s">
+        <v>1215</v>
       </c>
       <c r="B617" t="s">
         <v>973</v>
@@ -36362,7 +36379,7 @@
     </row>
     <row r="618" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B618" t="s">
         <v>973</v>
@@ -36412,7 +36429,7 @@
     </row>
     <row r="619" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B619" t="s">
         <v>973</v>
@@ -36462,7 +36479,7 @@
     </row>
     <row r="620" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B620" t="s">
         <v>973</v>
@@ -36512,7 +36529,7 @@
     </row>
     <row r="621" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
-        <v>1076</v>
+        <v>999</v>
       </c>
       <c r="B621" t="s">
         <v>973</v>
@@ -36561,8 +36578,8 @@
       </c>
     </row>
     <row r="622" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A622" s="1" t="s">
-        <v>1216</v>
+      <c r="A622" t="s">
+        <v>1076</v>
       </c>
       <c r="B622" t="s">
         <v>973</v>
@@ -36611,8 +36628,8 @@
       </c>
     </row>
     <row r="623" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A623" t="s">
-        <v>1000</v>
+      <c r="A623" s="1" t="s">
+        <v>1216</v>
       </c>
       <c r="B623" t="s">
         <v>973</v>
@@ -36662,7 +36679,7 @@
     </row>
     <row r="624" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B624" t="s">
         <v>973</v>
@@ -36712,7 +36729,7 @@
     </row>
     <row r="625" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B625" t="s">
         <v>973</v>
@@ -36762,7 +36779,7 @@
     </row>
     <row r="626" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B626" t="s">
         <v>973</v>
@@ -36812,7 +36829,7 @@
     </row>
     <row r="627" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="B627" t="s">
         <v>973</v>
@@ -36862,7 +36879,7 @@
     </row>
     <row r="628" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B628" t="s">
         <v>973</v>
@@ -36912,7 +36929,7 @@
     </row>
     <row r="629" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B629" t="s">
         <v>973</v>
@@ -36962,7 +36979,7 @@
     </row>
     <row r="630" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="B630" t="s">
         <v>973</v>
@@ -37012,7 +37029,7 @@
     </row>
     <row r="631" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
-        <v>1474</v>
+        <v>1004</v>
       </c>
       <c r="B631" t="s">
         <v>973</v>
@@ -37062,22 +37079,22 @@
     </row>
     <row r="632" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
-        <v>1525</v>
+        <v>1474</v>
       </c>
       <c r="B632" t="s">
-        <v>1009</v>
+        <v>973</v>
       </c>
       <c r="C632" t="s">
         <v>17</v>
       </c>
       <c r="D632" t="s">
-        <v>18</v>
-      </c>
-      <c r="E632" t="s">
-        <v>442</v>
-      </c>
-      <c r="F632" t="s">
-        <v>443</v>
+        <v>103</v>
+      </c>
+      <c r="E632" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F632" t="e">
+        <v>#N/A</v>
       </c>
       <c r="G632" t="e">
         <v>#N/A</v>
@@ -37086,33 +37103,33 @@
         <v>#N/A</v>
       </c>
       <c r="I632" t="s">
-        <v>447</v>
+        <v>974</v>
       </c>
       <c r="J632" t="b">
         <v>0</v>
       </c>
       <c r="K632" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="L632" t="s">
-        <v>447</v>
+        <v>110</v>
       </c>
       <c r="M632">
         <v>1</v>
       </c>
       <c r="N632" t="s">
-        <v>447</v>
+        <v>973</v>
       </c>
       <c r="O632" t="s">
-        <v>26</v>
+        <v>973</v>
       </c>
       <c r="P632" t="s">
-        <v>1341</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="633" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
-        <v>1008</v>
+        <v>1525</v>
       </c>
       <c r="B633" t="s">
         <v>1009</v>
@@ -37162,7 +37179,7 @@
     </row>
     <row r="634" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B634" t="s">
         <v>1009</v>
@@ -37212,22 +37229,22 @@
     </row>
     <row r="635" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
-        <v>1350</v>
+        <v>1010</v>
       </c>
       <c r="B635" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="C635" t="s">
         <v>17</v>
       </c>
       <c r="D635" t="s">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="E635" t="s">
-        <v>236</v>
-      </c>
-      <c r="F635" t="e">
-        <v>#N/A</v>
+        <v>442</v>
+      </c>
+      <c r="F635" t="s">
+        <v>443</v>
       </c>
       <c r="G635" t="e">
         <v>#N/A</v>
@@ -37236,33 +37253,33 @@
         <v>#N/A</v>
       </c>
       <c r="I635" t="s">
-        <v>241</v>
+        <v>447</v>
       </c>
       <c r="J635" t="b">
         <v>0</v>
       </c>
       <c r="K635" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="L635" t="s">
-        <v>241</v>
+        <v>447</v>
       </c>
       <c r="M635">
         <v>1</v>
       </c>
       <c r="N635" t="s">
-        <v>241</v>
+        <v>447</v>
       </c>
       <c r="O635" t="s">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="P635" t="s">
-        <v>1356</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="636" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
-        <v>1011</v>
+        <v>1350</v>
       </c>
       <c r="B636" t="s">
         <v>1012</v>
@@ -37312,7 +37329,7 @@
     </row>
     <row r="637" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="B637" t="s">
         <v>1012</v>
@@ -37362,7 +37379,7 @@
     </row>
     <row r="638" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B638" t="s">
         <v>1012</v>
@@ -37411,61 +37428,61 @@
       </c>
     </row>
     <row r="639" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A639" s="1" t="s">
+      <c r="A639" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B639" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C639" t="s">
+        <v>17</v>
+      </c>
+      <c r="D639" t="s">
+        <v>123</v>
+      </c>
+      <c r="E639" t="s">
+        <v>236</v>
+      </c>
+      <c r="F639" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G639" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H639" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I639" t="s">
+        <v>241</v>
+      </c>
+      <c r="J639" t="b">
+        <v>0</v>
+      </c>
+      <c r="K639" t="s">
+        <v>109</v>
+      </c>
+      <c r="L639" t="s">
+        <v>241</v>
+      </c>
+      <c r="M639">
+        <v>1</v>
+      </c>
+      <c r="N639" t="s">
+        <v>241</v>
+      </c>
+      <c r="O639" t="s">
+        <v>95</v>
+      </c>
+      <c r="P639" t="s">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="640" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A640" s="1" t="s">
         <v>1219</v>
       </c>
-      <c r="B639" t="s">
+      <c r="B640" t="s">
         <v>1281</v>
-      </c>
-      <c r="C639" t="s">
-        <v>17</v>
-      </c>
-      <c r="D639" t="s">
-        <v>18</v>
-      </c>
-      <c r="E639" t="s">
-        <v>19</v>
-      </c>
-      <c r="F639" t="s">
-        <v>379</v>
-      </c>
-      <c r="G639" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H639" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I639" t="s">
-        <v>383</v>
-      </c>
-      <c r="J639" t="b">
-        <v>0</v>
-      </c>
-      <c r="K639" t="s">
-        <v>24</v>
-      </c>
-      <c r="L639" t="s">
-        <v>383</v>
-      </c>
-      <c r="M639">
-        <v>1</v>
-      </c>
-      <c r="N639" t="s">
-        <v>383</v>
-      </c>
-      <c r="O639" t="s">
-        <v>26</v>
-      </c>
-      <c r="P639" t="s">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="640" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A640" t="s">
-        <v>1016</v>
-      </c>
-      <c r="B640" t="s">
-        <v>1017</v>
       </c>
       <c r="C640" t="s">
         <v>17</v>
@@ -37474,19 +37491,19 @@
         <v>18</v>
       </c>
       <c r="E640" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="F640" t="s">
-        <v>1018</v>
-      </c>
-      <c r="G640" t="s">
-        <v>1371</v>
-      </c>
-      <c r="H640" t="s">
-        <v>262</v>
+        <v>379</v>
+      </c>
+      <c r="G640" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H640" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I640" t="s">
-        <v>1019</v>
+        <v>383</v>
       </c>
       <c r="J640" t="b">
         <v>0</v>
@@ -37495,74 +37512,74 @@
         <v>24</v>
       </c>
       <c r="L640" t="s">
-        <v>1020</v>
+        <v>383</v>
       </c>
       <c r="M640">
         <v>1</v>
       </c>
       <c r="N640" t="s">
-        <v>1020</v>
+        <v>383</v>
       </c>
       <c r="O640" t="s">
         <v>26</v>
       </c>
       <c r="P640" t="s">
-        <v>1331</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="641" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
-        <v>1540</v>
+        <v>1016</v>
       </c>
       <c r="B641" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="C641" t="s">
         <v>17</v>
       </c>
       <c r="D641" t="s">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="E641" t="s">
-        <v>124</v>
+        <v>43</v>
       </c>
       <c r="F641" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="G641" t="s">
-        <v>1024</v>
+        <v>1371</v>
       </c>
       <c r="H641" t="s">
-        <v>1025</v>
+        <v>262</v>
       </c>
       <c r="I641" t="s">
-        <v>1026</v>
+        <v>1019</v>
       </c>
       <c r="J641" t="b">
         <v>0</v>
       </c>
       <c r="K641" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="L641" t="s">
-        <v>1027</v>
+        <v>1020</v>
       </c>
       <c r="M641">
         <v>1</v>
       </c>
       <c r="N641" t="s">
-        <v>1027</v>
+        <v>1020</v>
       </c>
       <c r="O641" t="s">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="P641" t="s">
-        <v>1313</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="642" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
-        <v>1021</v>
+        <v>1540</v>
       </c>
       <c r="B642" t="s">
         <v>1022</v>
@@ -37612,7 +37629,7 @@
     </row>
     <row r="643" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
-        <v>1028</v>
+        <v>1021</v>
       </c>
       <c r="B643" t="s">
         <v>1022</v>
@@ -37662,7 +37679,7 @@
     </row>
     <row r="644" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
-        <v>1397</v>
+        <v>1028</v>
       </c>
       <c r="B644" t="s">
         <v>1022</v>
@@ -37712,10 +37729,10 @@
     </row>
     <row r="645" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
-        <v>1034</v>
+        <v>1397</v>
       </c>
       <c r="B645" t="s">
-        <v>1030</v>
+        <v>1022</v>
       </c>
       <c r="C645" t="s">
         <v>17</v>
@@ -37733,10 +37750,10 @@
         <v>1024</v>
       </c>
       <c r="H645" t="s">
-        <v>1031</v>
+        <v>1025</v>
       </c>
       <c r="I645" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="J645" t="b">
         <v>0</v>
@@ -37762,7 +37779,7 @@
     </row>
     <row r="646" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
-        <v>1029</v>
+        <v>1034</v>
       </c>
       <c r="B646" t="s">
         <v>1030</v>
@@ -37812,7 +37829,7 @@
     </row>
     <row r="647" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
       <c r="B647" t="s">
         <v>1030</v>
@@ -37862,10 +37879,10 @@
     </row>
     <row r="648" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="B648" t="s">
-        <v>1036</v>
+        <v>1030</v>
       </c>
       <c r="C648" t="s">
         <v>17</v>
@@ -37883,10 +37900,10 @@
         <v>1024</v>
       </c>
       <c r="H648" t="s">
-        <v>710</v>
+        <v>1031</v>
       </c>
       <c r="I648" t="s">
-        <v>1027</v>
+        <v>1032</v>
       </c>
       <c r="J648" t="b">
         <v>0</v>
@@ -37911,8 +37928,8 @@
       </c>
     </row>
     <row r="649" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A649" s="1" t="s">
-        <v>1200</v>
+      <c r="A649" t="s">
+        <v>1035</v>
       </c>
       <c r="B649" t="s">
         <v>1036</v>
@@ -37961,8 +37978,8 @@
       </c>
     </row>
     <row r="650" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A650" t="s">
-        <v>1037</v>
+      <c r="A650" s="1" t="s">
+        <v>1200</v>
       </c>
       <c r="B650" t="s">
         <v>1036</v>
@@ -38012,7 +38029,7 @@
     </row>
     <row r="651" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B651" t="s">
         <v>1036</v>
@@ -38062,7 +38079,7 @@
     </row>
     <row r="652" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B652" t="s">
         <v>1036</v>
@@ -38112,7 +38129,7 @@
     </row>
     <row r="653" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B653" t="s">
         <v>1036</v>
@@ -38162,7 +38179,7 @@
     </row>
     <row r="654" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B654" t="s">
         <v>1036</v>
@@ -38212,7 +38229,7 @@
     </row>
     <row r="655" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B655" t="s">
         <v>1036</v>
@@ -38262,7 +38279,7 @@
     </row>
     <row r="656" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B656" t="s">
         <v>1036</v>
@@ -38312,7 +38329,7 @@
     </row>
     <row r="657" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B657" t="s">
         <v>1036</v>
@@ -38362,10 +38379,10 @@
     </row>
     <row r="658" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B658" t="s">
-        <v>1046</v>
+        <v>1036</v>
       </c>
       <c r="C658" t="s">
         <v>17</v>
@@ -38377,16 +38394,16 @@
         <v>124</v>
       </c>
       <c r="F658" t="s">
-        <v>190</v>
+        <v>1023</v>
       </c>
       <c r="G658" t="s">
-        <v>1047</v>
+        <v>1024</v>
       </c>
       <c r="H658" t="s">
-        <v>643</v>
+        <v>710</v>
       </c>
       <c r="I658" t="s">
-        <v>1048</v>
+        <v>1027</v>
       </c>
       <c r="J658" t="b">
         <v>0</v>
@@ -38395,79 +38412,129 @@
         <v>109</v>
       </c>
       <c r="L658" t="s">
-        <v>194</v>
+        <v>1027</v>
       </c>
       <c r="M658">
         <v>1</v>
       </c>
       <c r="N658" t="s">
-        <v>194</v>
+        <v>1027</v>
       </c>
       <c r="O658" t="s">
         <v>95</v>
       </c>
       <c r="P658" t="s">
-        <v>1320</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="659" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B659" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C659" t="s">
+        <v>17</v>
+      </c>
+      <c r="D659" t="s">
+        <v>123</v>
+      </c>
+      <c r="E659" t="s">
+        <v>124</v>
+      </c>
+      <c r="F659" t="s">
+        <v>190</v>
+      </c>
+      <c r="G659" t="s">
+        <v>1047</v>
+      </c>
+      <c r="H659" t="s">
+        <v>643</v>
+      </c>
+      <c r="I659" t="s">
+        <v>1048</v>
+      </c>
+      <c r="J659" t="b">
+        <v>0</v>
+      </c>
+      <c r="K659" t="s">
+        <v>109</v>
+      </c>
+      <c r="L659" t="s">
+        <v>194</v>
+      </c>
+      <c r="M659">
+        <v>1</v>
+      </c>
+      <c r="N659" t="s">
+        <v>194</v>
+      </c>
+      <c r="O659" t="s">
+        <v>95</v>
+      </c>
+      <c r="P659" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="660" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A660" t="s">
         <v>1049</v>
       </c>
-      <c r="B659" t="s">
+      <c r="B660" t="s">
         <v>1050</v>
       </c>
-      <c r="C659" t="s">
-        <v>17</v>
-      </c>
-      <c r="D659" t="s">
+      <c r="C660" t="s">
+        <v>17</v>
+      </c>
+      <c r="D660" t="s">
         <v>18</v>
       </c>
-      <c r="E659" t="s">
+      <c r="E660" t="s">
         <v>49</v>
       </c>
-      <c r="F659" t="s">
+      <c r="F660" t="s">
         <v>50</v>
       </c>
-      <c r="G659" t="s">
+      <c r="G660" t="s">
         <v>1051</v>
       </c>
-      <c r="H659" t="s">
+      <c r="H660" t="s">
         <v>1052</v>
       </c>
-      <c r="I659" t="s">
+      <c r="I660" t="s">
         <v>1053</v>
       </c>
-      <c r="J659" t="b">
-        <v>0</v>
-      </c>
-      <c r="K659" t="s">
+      <c r="J660" t="b">
+        <v>0</v>
+      </c>
+      <c r="K660" t="s">
         <v>24</v>
       </c>
-      <c r="L659" t="s">
+      <c r="L660" t="s">
         <v>54</v>
       </c>
-      <c r="M659">
-        <v>1</v>
-      </c>
-      <c r="N659" t="s">
+      <c r="M660">
+        <v>1</v>
+      </c>
+      <c r="N660" t="s">
         <v>54</v>
       </c>
-      <c r="O659" t="s">
+      <c r="O660" t="s">
         <v>26</v>
       </c>
-      <c r="P659" t="s">
+      <c r="P660" t="s">
         <v>1336</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P659" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P659">
-      <sortCondition ref="B1:B659"/>
+  <autoFilter ref="A1:P660" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P660">
+      <sortCondition ref="B1:B660"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O628">
-    <sortCondition ref="A1:A628"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O629">
+    <sortCondition ref="A1:A629"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -38476,7 +38543,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="3" bestFit="1" customWidth="1"/>
@@ -38869,6 +38936,17 @@
         <v>1598</v>
       </c>
     </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="6">
+        <v>46217</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>1605</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
